--- a/data_raw/precio_leche_productor.xlsx
+++ b/data_raw/precio_leche_productor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/1- Producción y precios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1225" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B5219C-3642-4916-9173-FD9CB3504D4E}"/>
+  <xr:revisionPtr revIDLastSave="1234" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D32E48E1-1C71-42DE-84CB-53937A08B4A4}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16200" windowWidth="28410" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Precio en tambo" sheetId="1" r:id="rId1"/>
@@ -2896,6 +2896,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2962,9 +2965,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="62">
@@ -4789,17 +4789,17 @@
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="351" t="s">
+      <c r="E10" s="352" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="352"/>
-      <c r="G10" s="352"/>
-      <c r="H10" s="352"/>
-      <c r="I10" s="352"/>
-      <c r="J10" s="352"/>
-      <c r="K10" s="352"/>
-      <c r="L10" s="352"/>
-      <c r="M10" s="353"/>
+      <c r="F10" s="353"/>
+      <c r="G10" s="353"/>
+      <c r="H10" s="353"/>
+      <c r="I10" s="353"/>
+      <c r="J10" s="353"/>
+      <c r="K10" s="353"/>
+      <c r="L10" s="353"/>
+      <c r="M10" s="354"/>
       <c r="N10" s="17"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -4809,17 +4809,17 @@
       <c r="T10" s="19"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="348" t="s">
+      <c r="W10" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="349"/>
-      <c r="Y10" s="349"/>
-      <c r="Z10" s="349"/>
-      <c r="AA10" s="349"/>
-      <c r="AB10" s="349"/>
-      <c r="AC10" s="349"/>
-      <c r="AD10" s="349"/>
-      <c r="AE10" s="350"/>
+      <c r="X10" s="350"/>
+      <c r="Y10" s="350"/>
+      <c r="Z10" s="350"/>
+      <c r="AA10" s="350"/>
+      <c r="AB10" s="350"/>
+      <c r="AC10" s="350"/>
+      <c r="AD10" s="350"/>
+      <c r="AE10" s="351"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
@@ -7629,12 +7629,11 @@
         <v>16.666737003816007</v>
       </c>
       <c r="O36" s="311">
-        <f t="shared" ref="O36" si="14">AVERAGE(C36:N36)</f>
-        <v>17.615334273122638</v>
+        <v>17.531654337842706</v>
       </c>
       <c r="P36" s="302">
-        <f t="shared" ref="P36" si="15">O36/O35-1</f>
-        <v>9.6966736791528341E-2</v>
+        <f t="shared" ref="P36" si="14">O36/O35-1</f>
+        <v>9.1755702807404083E-2</v>
       </c>
       <c r="Q36" s="288">
         <v>17.54025600489415</v>
@@ -7684,18 +7683,17 @@
         <v>16.66</v>
       </c>
       <c r="AG36" s="311">
-        <f t="shared" ref="AG36" si="16">AVERAGE(U36:AF36)</f>
-        <v>17.333333333333332</v>
+        <v>17.300494927115889</v>
       </c>
       <c r="AH36" s="302">
-        <f t="shared" ref="AH36:AJ36" si="17">AG36/AG35-1</f>
-        <v>0.11954357069809984</v>
+        <f t="shared" ref="AH36:AJ36" si="15">AG36/AG35-1</f>
+        <v>0.11742256916621274</v>
       </c>
       <c r="AI36" s="288">
         <v>17.315775047264474</v>
       </c>
       <c r="AJ36" s="302">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.11761099371635853</v>
       </c>
       <c r="AK36" s="268"/>
@@ -8051,23 +8049,23 @@
     </row>
     <row r="45" spans="1:37" ht="36" customHeight="1">
       <c r="A45" s="68"/>
-      <c r="B45" s="354"/>
-      <c r="C45" s="355"/>
-      <c r="D45" s="355"/>
-      <c r="E45" s="356"/>
-      <c r="F45" s="356"/>
-      <c r="G45" s="356"/>
-      <c r="H45" s="356"/>
-      <c r="I45" s="356"/>
-      <c r="J45" s="356"/>
-      <c r="K45" s="356"/>
-      <c r="L45" s="356"/>
-      <c r="M45" s="356"/>
-      <c r="N45" s="355"/>
-      <c r="O45" s="355"/>
-      <c r="P45" s="355"/>
-      <c r="Q45" s="355"/>
-      <c r="R45" s="355"/>
+      <c r="B45" s="355"/>
+      <c r="C45" s="356"/>
+      <c r="D45" s="356"/>
+      <c r="E45" s="357"/>
+      <c r="F45" s="357"/>
+      <c r="G45" s="357"/>
+      <c r="H45" s="357"/>
+      <c r="I45" s="357"/>
+      <c r="J45" s="357"/>
+      <c r="K45" s="357"/>
+      <c r="L45" s="357"/>
+      <c r="M45" s="357"/>
+      <c r="N45" s="356"/>
+      <c r="O45" s="356"/>
+      <c r="P45" s="356"/>
+      <c r="Q45" s="356"/>
+      <c r="R45" s="356"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
@@ -8093,17 +8091,17 @@
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="69"/>
-      <c r="E46" s="351" t="s">
+      <c r="E46" s="352" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="352"/>
-      <c r="G46" s="352"/>
-      <c r="H46" s="352"/>
-      <c r="I46" s="352"/>
-      <c r="J46" s="352"/>
-      <c r="K46" s="352"/>
-      <c r="L46" s="352"/>
-      <c r="M46" s="353"/>
+      <c r="F46" s="353"/>
+      <c r="G46" s="353"/>
+      <c r="H46" s="353"/>
+      <c r="I46" s="353"/>
+      <c r="J46" s="353"/>
+      <c r="K46" s="353"/>
+      <c r="L46" s="353"/>
+      <c r="M46" s="354"/>
       <c r="N46" s="70"/>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -8113,17 +8111,17 @@
       <c r="T46" s="71"/>
       <c r="U46" s="7"/>
       <c r="V46" s="69"/>
-      <c r="W46" s="348" t="s">
+      <c r="W46" s="349" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="349"/>
-      <c r="Y46" s="349"/>
-      <c r="Z46" s="349"/>
-      <c r="AA46" s="349"/>
-      <c r="AB46" s="349"/>
-      <c r="AC46" s="349"/>
-      <c r="AD46" s="349"/>
-      <c r="AE46" s="350"/>
+      <c r="X46" s="350"/>
+      <c r="Y46" s="350"/>
+      <c r="Z46" s="350"/>
+      <c r="AA46" s="350"/>
+      <c r="AB46" s="350"/>
+      <c r="AC46" s="350"/>
+      <c r="AD46" s="350"/>
+      <c r="AE46" s="351"/>
       <c r="AF46" s="70"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="7"/>
@@ -8319,7 +8317,7 @@
         <v>9.9787452610928404E-2</v>
       </c>
       <c r="O49" s="308">
-        <f t="shared" ref="O49:O68" si="18">AVERAGE(C49:N49)</f>
+        <f t="shared" ref="O49:O68" si="16">AVERAGE(C49:N49)</f>
         <v>0.1123925762896878</v>
       </c>
       <c r="P49" s="309"/>
@@ -8368,7 +8366,7 @@
         <v>9.9787452610928404E-2</v>
       </c>
       <c r="AG49" s="308">
-        <f t="shared" ref="AG49:AG70" si="19">AVERAGE(U49:AF49)</f>
+        <f t="shared" ref="AG49:AG70" si="17">AVERAGE(U49:AF49)</f>
         <v>0.1123925762896878</v>
       </c>
       <c r="AH49" s="309"/>
@@ -8420,18 +8418,18 @@
         <v>0.12726941438463199</v>
       </c>
       <c r="O50" s="310">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0.12607327169791874</v>
       </c>
       <c r="P50" s="301">
-        <f t="shared" ref="P50:P68" si="20">O50/O49-1</f>
+        <f t="shared" ref="P50:P68" si="18">O50/O49-1</f>
         <v>0.121722411389249</v>
       </c>
       <c r="Q50" s="109">
         <v>0.12691891171451999</v>
       </c>
       <c r="R50" s="301">
-        <f t="shared" ref="R50:R68" si="21">Q50/Q49-1</f>
+        <f t="shared" ref="R50:R68" si="19">Q50/Q49-1</f>
         <v>0.14270455687955241</v>
       </c>
       <c r="S50" s="7"/>
@@ -8475,18 +8473,18 @@
         <v>0.12726941438463199</v>
       </c>
       <c r="AG50" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.12607327169791874</v>
       </c>
       <c r="AH50" s="301">
-        <f t="shared" ref="AH50:AJ71" si="22">AG50/AG49-1</f>
+        <f t="shared" ref="AH50:AJ71" si="20">AG50/AG49-1</f>
         <v>0.121722411389249</v>
       </c>
       <c r="AI50" s="109">
         <v>0.12691891171451999</v>
       </c>
       <c r="AJ50" s="301">
-        <f t="shared" ref="AJ50:AJ68" si="23">AI50/AI49-1</f>
+        <f t="shared" ref="AJ50:AJ68" si="21">AI50/AI49-1</f>
         <v>0.14270455687955241</v>
       </c>
       <c r="AK50" s="9"/>
@@ -8533,18 +8531,18 @@
         <v>0.15406206254107899</v>
       </c>
       <c r="O51" s="310">
+        <f t="shared" si="16"/>
+        <v>0.14574238407361026</v>
+      </c>
+      <c r="P51" s="301">
         <f t="shared" si="18"/>
-        <v>0.14574238407361026</v>
-      </c>
-      <c r="P51" s="301">
-        <f t="shared" si="20"/>
         <v>0.15601334137516654</v>
       </c>
       <c r="Q51" s="109">
         <v>0.14691818383174399</v>
       </c>
       <c r="R51" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.15757519385454999</v>
       </c>
       <c r="S51" s="7"/>
@@ -8588,18 +8586,18 @@
         <v>0.15406206254107899</v>
       </c>
       <c r="AG51" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.14574238407361026</v>
       </c>
       <c r="AH51" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.15601334137516654</v>
       </c>
       <c r="AI51" s="109">
         <v>0.14691818383174399</v>
       </c>
       <c r="AJ51" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.15757519385454999</v>
       </c>
       <c r="AK51" s="9"/>
@@ -8646,18 +8644,18 @@
         <v>0.17543486228190999</v>
       </c>
       <c r="O52" s="310">
+        <f t="shared" si="16"/>
+        <v>0.17279418487470519</v>
+      </c>
+      <c r="P52" s="301">
         <f t="shared" si="18"/>
-        <v>0.17279418487470519</v>
-      </c>
-      <c r="P52" s="301">
-        <f t="shared" si="20"/>
         <v>0.18561382107919844</v>
       </c>
       <c r="Q52" s="109">
         <v>0.17319959752118</v>
       </c>
       <c r="R52" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.17888468945092884</v>
       </c>
       <c r="S52" s="7"/>
@@ -8701,18 +8699,18 @@
         <v>0.17543486228190999</v>
       </c>
       <c r="AG52" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.17279418487470519</v>
       </c>
       <c r="AH52" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.18561382107919844</v>
       </c>
       <c r="AI52" s="109">
         <v>0.17319959752118</v>
       </c>
       <c r="AJ52" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.17888468945092884</v>
       </c>
       <c r="AK52" s="9"/>
@@ -8759,18 +8757,18 @@
         <v>0.15221883404297701</v>
       </c>
       <c r="O53" s="310">
+        <f t="shared" si="16"/>
+        <v>0.17157503060509141</v>
+      </c>
+      <c r="P53" s="301">
         <f t="shared" si="18"/>
-        <v>0.17157503060509141</v>
-      </c>
-      <c r="P53" s="301">
-        <f t="shared" si="20"/>
         <v>-7.0555283471940289E-3</v>
       </c>
       <c r="Q53" s="109">
         <v>0.17005578456324</v>
       </c>
       <c r="R53" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-1.8151387202591795E-2</v>
       </c>
       <c r="S53" s="7"/>
@@ -8814,18 +8812,18 @@
         <v>0.15221883404297701</v>
       </c>
       <c r="AG53" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.17157503060509141</v>
       </c>
       <c r="AH53" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-7.0555283471940289E-3</v>
       </c>
       <c r="AI53" s="109">
         <v>0.17005578456324</v>
       </c>
       <c r="AJ53" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-1.8151387202591795E-2</v>
       </c>
       <c r="AK53" s="9"/>
@@ -8872,18 +8870,18 @@
         <v>0.34739999999999999</v>
       </c>
       <c r="O54" s="310">
+        <f t="shared" si="16"/>
+        <v>0.25817706117545897</v>
+      </c>
+      <c r="P54" s="301">
         <f t="shared" si="18"/>
-        <v>0.25817706117545897</v>
-      </c>
-      <c r="P54" s="301">
-        <f t="shared" si="20"/>
         <v>0.50474728324365903</v>
       </c>
       <c r="Q54" s="109">
         <v>0.26607669681185703</v>
       </c>
       <c r="R54" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.56464361089057191</v>
       </c>
       <c r="S54" s="7"/>
@@ -8927,18 +8925,18 @@
         <v>0.34739999999999999</v>
       </c>
       <c r="AG54" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.25817706117545897</v>
       </c>
       <c r="AH54" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.50474728324365903</v>
       </c>
       <c r="AI54" s="109">
         <v>0.26607669681185703</v>
       </c>
       <c r="AJ54" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.56464361089057191</v>
       </c>
       <c r="AK54" s="9"/>
@@ -8985,18 +8983,18 @@
         <v>0.19545846507617101</v>
       </c>
       <c r="O55" s="310">
+        <f t="shared" si="16"/>
+        <v>0.35016013743502383</v>
+      </c>
+      <c r="P55" s="301">
         <f t="shared" si="18"/>
-        <v>0.35016013743502383</v>
-      </c>
-      <c r="P55" s="301">
-        <f t="shared" si="20"/>
         <v>0.35627904292028689</v>
       </c>
       <c r="Q55" s="109">
         <v>0.33952464426128998</v>
       </c>
       <c r="R55" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.27604051136191021</v>
       </c>
       <c r="S55" s="7"/>
@@ -9040,18 +9038,18 @@
         <v>0.19545846507617101</v>
       </c>
       <c r="AG55" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.35016013743502383</v>
       </c>
       <c r="AH55" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.35627904292028689</v>
       </c>
       <c r="AI55" s="109">
         <v>0.33952464426128998</v>
       </c>
       <c r="AJ55" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.27604051136191021</v>
       </c>
       <c r="AK55" s="9"/>
@@ -9098,18 +9096,18 @@
         <v>0.28016038166776602</v>
       </c>
       <c r="O56" s="310">
+        <f t="shared" si="16"/>
+        <v>0.22706280750772864</v>
+      </c>
+      <c r="P56" s="301">
         <f t="shared" si="18"/>
-        <v>0.22706280750772864</v>
-      </c>
-      <c r="P56" s="301">
-        <f t="shared" si="20"/>
         <v>-0.35154581223608672</v>
       </c>
       <c r="Q56" s="109">
         <v>0.230222803200861</v>
       </c>
       <c r="R56" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-0.32192608963110469</v>
       </c>
       <c r="S56" s="7"/>
@@ -9153,18 +9151,18 @@
         <v>0.28016038166776602</v>
       </c>
       <c r="AG56" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.22706280750772864</v>
       </c>
       <c r="AH56" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-0.35154581223608672</v>
       </c>
       <c r="AI56" s="109">
         <v>0.230222803200861</v>
       </c>
       <c r="AJ56" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-0.32192608963110469</v>
       </c>
       <c r="AK56" s="9"/>
@@ -9211,18 +9209,18 @@
         <v>0.34142678347934902</v>
       </c>
       <c r="O57" s="310">
+        <f t="shared" si="16"/>
+        <v>0.31984518389594646</v>
+      </c>
+      <c r="P57" s="301">
         <f t="shared" si="18"/>
-        <v>0.31984518389594646</v>
-      </c>
-      <c r="P57" s="301">
-        <f t="shared" si="20"/>
         <v>0.40861987661744092</v>
       </c>
       <c r="Q57" s="109">
         <v>0.32018425988215998</v>
       </c>
       <c r="R57" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.3907582369362903</v>
       </c>
       <c r="S57" s="7"/>
@@ -9266,18 +9264,18 @@
         <v>0.34142678347934902</v>
       </c>
       <c r="AG57" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.31984518389594646</v>
       </c>
       <c r="AH57" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.40861987661744092</v>
       </c>
       <c r="AI57" s="109">
         <v>0.32018425988215998</v>
       </c>
       <c r="AJ57" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.3907582369362903</v>
       </c>
       <c r="AK57" s="9"/>
@@ -9324,18 +9322,18 @@
         <v>0.37756634952428603</v>
       </c>
       <c r="O58" s="310">
+        <f t="shared" si="16"/>
+        <v>0.40988489993539617</v>
+      </c>
+      <c r="P58" s="301">
         <f t="shared" si="18"/>
-        <v>0.40988489993539617</v>
-      </c>
-      <c r="P58" s="301">
-        <f t="shared" si="20"/>
         <v>0.28151030740153926</v>
       </c>
       <c r="Q58" s="109">
         <v>0.40811971389561402</v>
       </c>
       <c r="R58" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.27464015266027642</v>
       </c>
       <c r="S58" s="7"/>
@@ -9379,18 +9377,18 @@
         <v>0.37756634952428603</v>
       </c>
       <c r="AG58" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.40988489993539617</v>
       </c>
       <c r="AH58" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.28151030740153926</v>
       </c>
       <c r="AI58" s="109">
         <v>0.40811971389561402</v>
       </c>
       <c r="AJ58" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.27464015266027642</v>
       </c>
       <c r="AK58" s="9"/>
@@ -9437,18 +9435,18 @@
         <v>0.36158309158723601</v>
       </c>
       <c r="O59" s="310">
+        <f t="shared" si="16"/>
+        <v>0.37623027710926316</v>
+      </c>
+      <c r="P59" s="301">
         <f t="shared" si="18"/>
-        <v>0.37623027710926316</v>
-      </c>
-      <c r="P59" s="301">
-        <f t="shared" si="20"/>
         <v>-8.2107496107901246E-2</v>
       </c>
       <c r="Q59" s="109">
         <v>0.37415475605069098</v>
       </c>
       <c r="R59" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-8.3223026696550018E-2</v>
       </c>
       <c r="S59" s="7"/>
@@ -9492,18 +9490,18 @@
         <v>0.36158309158723601</v>
       </c>
       <c r="AG59" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.37623027710926316</v>
       </c>
       <c r="AH59" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-8.2107496107901246E-2</v>
       </c>
       <c r="AI59" s="109">
         <v>0.37415475605069098</v>
       </c>
       <c r="AJ59" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-8.3223026696550018E-2</v>
       </c>
       <c r="AK59" s="9"/>
@@ -9550,18 +9548,18 @@
         <v>0.43626831437532199</v>
       </c>
       <c r="O60" s="310">
+        <f t="shared" si="16"/>
+        <v>0.41706190783437663</v>
+      </c>
+      <c r="P60" s="301">
         <f t="shared" si="18"/>
-        <v>0.41706190783437663</v>
-      </c>
-      <c r="P60" s="301">
-        <f t="shared" si="20"/>
         <v>0.10852829559290189</v>
       </c>
       <c r="Q60" s="109">
         <v>0.41937677654780298</v>
       </c>
       <c r="R60" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.12086448124953209</v>
       </c>
       <c r="S60" s="7"/>
@@ -9605,18 +9603,18 @@
         <v>0.43626831437532199</v>
       </c>
       <c r="AG60" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.41706190783437663</v>
       </c>
       <c r="AH60" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.10852829559290189</v>
       </c>
       <c r="AI60" s="109">
         <v>0.41937677654780298</v>
       </c>
       <c r="AJ60" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.12086448124953209</v>
       </c>
       <c r="AK60" s="9"/>
@@ -9663,18 +9661,18 @@
         <v>0.37623926660306101</v>
       </c>
       <c r="O61" s="310">
+        <f t="shared" si="16"/>
+        <v>0.42728878975602091</v>
+      </c>
+      <c r="P61" s="301">
         <f t="shared" si="18"/>
-        <v>0.42728878975602091</v>
-      </c>
-      <c r="P61" s="301">
-        <f t="shared" si="20"/>
         <v>2.4521256268039693E-2</v>
       </c>
       <c r="Q61" s="109">
         <v>0.42264838225031998</v>
       </c>
       <c r="R61" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>7.8011131885937779E-3</v>
       </c>
       <c r="S61" s="7"/>
@@ -9718,18 +9716,18 @@
         <v>0.37623926660306101</v>
       </c>
       <c r="AG61" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.42728878975602091</v>
       </c>
       <c r="AH61" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>2.4521256268039693E-2</v>
       </c>
       <c r="AI61" s="109">
         <v>0.42264838225031998</v>
       </c>
       <c r="AJ61" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>7.8011131885937779E-3</v>
       </c>
       <c r="AK61" s="9"/>
@@ -9776,18 +9774,18 @@
         <v>0.25180230222905797</v>
       </c>
       <c r="O62" s="310">
+        <f t="shared" si="16"/>
+        <v>0.30198126267403297</v>
+      </c>
+      <c r="P62" s="301">
         <f t="shared" si="18"/>
-        <v>0.30198126267403297</v>
-      </c>
-      <c r="P62" s="301">
-        <f t="shared" si="20"/>
         <v>-0.2932619111152851</v>
       </c>
       <c r="Q62" s="109">
         <v>0.29484615928250701</v>
       </c>
       <c r="R62" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-0.30238427102773136</v>
       </c>
       <c r="S62" s="7"/>
@@ -9831,18 +9829,18 @@
         <v>0.25180230222905797</v>
       </c>
       <c r="AG62" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.30198126267403297</v>
       </c>
       <c r="AH62" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-0.2932619111152851</v>
       </c>
       <c r="AI62" s="109">
         <v>0.29484615928250701</v>
       </c>
       <c r="AJ62" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-0.30238427102773136</v>
       </c>
       <c r="AK62" s="9"/>
@@ -9889,18 +9887,18 @@
         <v>0.31310679611650499</v>
       </c>
       <c r="O63" s="310">
+        <f t="shared" si="16"/>
+        <v>0.280697814641022</v>
+      </c>
+      <c r="P63" s="301">
         <f t="shared" si="18"/>
-        <v>0.280697814641022</v>
-      </c>
-      <c r="P63" s="301">
-        <f t="shared" si="20"/>
         <v>-7.0479366317455661E-2</v>
       </c>
       <c r="Q63" s="109">
         <v>0.28465729192526501</v>
       </c>
       <c r="R63" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-3.45565544487203E-2</v>
       </c>
       <c r="S63" s="7"/>
@@ -9944,18 +9942,18 @@
         <v>0.31310679611650499</v>
       </c>
       <c r="AG63" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.28068374369017574</v>
       </c>
       <c r="AH63" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-7.0525961760900313E-2</v>
       </c>
       <c r="AI63" s="109">
         <v>0.28465729192526501</v>
       </c>
       <c r="AJ63" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-3.45565544487203E-2</v>
       </c>
       <c r="AK63" s="9"/>
@@ -10002,18 +10000,18 @@
         <v>0.33014515900907698</v>
       </c>
       <c r="O64" s="310">
+        <f t="shared" si="16"/>
+        <v>0.34158503910440524</v>
+      </c>
+      <c r="P64" s="301">
         <f t="shared" si="18"/>
-        <v>0.34158503910440524</v>
-      </c>
-      <c r="P64" s="301">
-        <f t="shared" si="20"/>
         <v>0.21691378160977326</v>
       </c>
       <c r="Q64" s="109">
         <v>0.33864532425546001</v>
       </c>
       <c r="R64" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.18965975529750079</v>
       </c>
       <c r="S64" s="7"/>
@@ -10057,18 +10055,18 @@
         <v>0.32548476454293601</v>
       </c>
       <c r="AG64" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.3396558141457085</v>
       </c>
       <c r="AH64" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.21010148176100762</v>
       </c>
       <c r="AI64" s="109">
         <v>0.33864532425546001</v>
       </c>
       <c r="AJ64" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.18965975529750079</v>
       </c>
       <c r="AK64" s="9"/>
@@ -10115,18 +10113,18 @@
         <v>0.29366114111876801</v>
       </c>
       <c r="O65" s="310">
+        <f t="shared" si="16"/>
+        <v>0.32510052452938304</v>
+      </c>
+      <c r="P65" s="301">
         <f t="shared" si="18"/>
-        <v>0.32510052452938304</v>
-      </c>
-      <c r="P65" s="301">
-        <f t="shared" si="20"/>
         <v>-4.8258889260029081E-2</v>
       </c>
       <c r="Q65" s="109">
         <v>0.32229745657187803</v>
       </c>
       <c r="R65" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-4.8274305040307719E-2</v>
       </c>
       <c r="S65" s="7"/>
@@ -10170,18 +10168,18 @@
         <v>0.29366114111876801</v>
       </c>
       <c r="AG65" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.32232426477271819</v>
       </c>
       <c r="AH65" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-5.1026800222990665E-2</v>
       </c>
       <c r="AI65" s="109">
         <v>0.319792087502487</v>
       </c>
       <c r="AJ65" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-5.5672514582693289E-2</v>
       </c>
       <c r="AK65" s="9"/>
@@ -10228,18 +10226,18 @@
         <v>0.31134761207928702</v>
       </c>
       <c r="O66" s="310">
+        <f t="shared" si="16"/>
+        <v>0.30388347724426534</v>
+      </c>
+      <c r="P66" s="301">
         <f t="shared" si="18"/>
-        <v>0.30388347724426534</v>
-      </c>
-      <c r="P66" s="301">
-        <f t="shared" si="20"/>
         <v>-6.5263036151146148E-2</v>
       </c>
       <c r="Q66" s="109">
         <v>0.30410499557590598</v>
       </c>
       <c r="R66" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-5.6446182323237837E-2</v>
       </c>
       <c r="S66" s="7"/>
@@ -10283,18 +10281,18 @@
         <v>0.30011972861513903</v>
       </c>
       <c r="AG66" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.30030095056130407</v>
       </c>
       <c r="AH66" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-6.8326578599174126E-2</v>
       </c>
       <c r="AI66" s="109">
         <v>0.30046525273006602</v>
       </c>
       <c r="AJ66" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-6.0435625294420925E-2</v>
       </c>
       <c r="AK66" s="9"/>
@@ -10341,18 +10339,18 @@
         <v>0.30718432420892799</v>
       </c>
       <c r="O67" s="310">
+        <f t="shared" si="16"/>
+        <v>0.29883788698993852</v>
+      </c>
+      <c r="P67" s="301">
         <f t="shared" si="18"/>
-        <v>0.29883788698993852</v>
-      </c>
-      <c r="P67" s="301">
-        <f t="shared" si="20"/>
         <v>-1.6603700537068389E-2</v>
       </c>
       <c r="Q67" s="109">
         <v>0.29874128780418102</v>
       </c>
       <c r="R67" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-1.7637683858390152E-2</v>
       </c>
       <c r="S67" s="7"/>
@@ -10396,18 +10394,18 @@
         <v>0.30238701764317399</v>
       </c>
       <c r="AG67" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.29431054299789616</v>
       </c>
       <c r="AH67" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-1.994801399133439E-2</v>
       </c>
       <c r="AI67" s="109">
         <v>0.29427909496996102</v>
       </c>
       <c r="AJ67" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-2.0588596198384934E-2</v>
       </c>
       <c r="AK67" s="9"/>
@@ -10454,18 +10452,18 @@
         <v>0.35563825152968298</v>
       </c>
       <c r="O68" s="310">
+        <f t="shared" si="16"/>
+        <v>0.34754642545719666</v>
+      </c>
+      <c r="P68" s="301">
         <f t="shared" si="18"/>
-        <v>0.34754642545719666</v>
-      </c>
-      <c r="P68" s="301">
-        <f t="shared" si="20"/>
         <v>0.16299318322009859</v>
       </c>
       <c r="Q68" s="109">
         <v>0.34930739892531898</v>
       </c>
       <c r="R68" s="301">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.16926388546026172</v>
       </c>
       <c r="S68" s="7"/>
@@ -10509,18 +10507,18 @@
         <v>0.35059221658206402</v>
       </c>
       <c r="AG68" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.34130711707315192</v>
       </c>
       <c r="AH68" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.15968362395903601</v>
       </c>
       <c r="AI68" s="109">
         <v>0.34281851132805602</v>
       </c>
       <c r="AJ68" s="301">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0.16494347436758883</v>
       </c>
       <c r="AK68" s="9"/>
@@ -10567,18 +10565,18 @@
         <v>0.41877718086467125</v>
       </c>
       <c r="O69" s="310">
-        <f t="shared" ref="O69:O70" si="24">AVERAGE(C69:N69)</f>
+        <f t="shared" ref="O69:O70" si="22">AVERAGE(C69:N69)</f>
         <v>0.41743976379395514</v>
       </c>
       <c r="P69" s="301">
-        <f t="shared" ref="P69:R71" si="25">O69/O68-1</f>
+        <f t="shared" ref="P69:R71" si="23">O69/O68-1</f>
         <v>0.2011050415633362</v>
       </c>
       <c r="Q69" s="109">
         <v>0.41771464653289508</v>
       </c>
       <c r="R69" s="301">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0.19583681255546903</v>
       </c>
       <c r="S69" s="7"/>
@@ -10622,18 +10620,18 @@
         <v>0.41877718086467125</v>
       </c>
       <c r="AG69" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.41742128709586246</v>
       </c>
       <c r="AH69" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.22300786070744927</v>
       </c>
       <c r="AI69" s="109">
         <v>0.41769963796243853</v>
       </c>
       <c r="AJ69" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0.21842789744433011</v>
       </c>
       <c r="AK69" s="9"/>
@@ -10680,18 +10678,18 @@
         <v>0.35760517976105632</v>
       </c>
       <c r="O70" s="310">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>0.41293831242055351</v>
       </c>
       <c r="P70" s="301">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-1.0783475279138699E-2</v>
       </c>
       <c r="Q70" s="109">
         <v>0.40869661057801471</v>
       </c>
       <c r="R70" s="301">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-2.1588986715528558E-2</v>
       </c>
       <c r="S70" s="7"/>
@@ -10735,18 +10733,18 @@
         <v>0.35760517976105632</v>
       </c>
       <c r="AG70" s="310">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.41230917455664856</v>
       </c>
       <c r="AH70" s="301">
-        <f t="shared" ref="AH70" si="26">AG70/AG69-1</f>
+        <f t="shared" ref="AH70" si="24">AG70/AG69-1</f>
         <v>-1.224688988618805E-2</v>
       </c>
       <c r="AI70" s="109">
         <v>0.40795872687437473</v>
       </c>
       <c r="AJ70" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-2.3320372350765006E-2</v>
       </c>
       <c r="AK70" s="9"/>
@@ -10793,7 +10791,7 @@
         <v>0.3920596711152291</v>
       </c>
       <c r="O71" s="310">
-        <f t="shared" ref="O71" si="27">AVERAGE(C71:N71)</f>
+        <f t="shared" ref="O71" si="25">AVERAGE(C71:N71)</f>
         <v>0.39957892641892118</v>
       </c>
       <c r="P71" s="301">
@@ -10804,7 +10802,7 @@
         <v>0.39658372155990007</v>
       </c>
       <c r="R71" s="301">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-2.9637850436252777E-2</v>
       </c>
       <c r="S71" s="7"/>
@@ -10848,18 +10846,18 @@
         <v>0.37389075763421575</v>
       </c>
       <c r="AG71" s="310">
-        <f t="shared" ref="AG71:AG72" si="28">AVERAGE(U71:AF71)</f>
+        <f t="shared" ref="AG71" si="26">AVERAGE(U71:AF71)</f>
         <v>0.38533965945345633</v>
       </c>
       <c r="AH71" s="301">
-        <f t="shared" ref="AH71" si="29">AG71/AG70-1</f>
+        <f t="shared" ref="AH71" si="27">AG71/AG70-1</f>
         <v>-6.5410902224507295E-2</v>
       </c>
       <c r="AI71" s="109">
         <v>0.38363202432610127</v>
       </c>
       <c r="AJ71" s="301">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>-5.9630303130553064E-2</v>
       </c>
       <c r="AK71" s="9"/>
@@ -10906,12 +10904,11 @@
         <v>0.42572574021854981</v>
       </c>
       <c r="O72" s="311">
-        <f t="shared" ref="O72" si="30">AVERAGE(C72:N72)</f>
-        <v>0.42889732760513088</v>
+        <v>0.42911807488608505</v>
       </c>
       <c r="P72" s="302">
         <f>+O72/O71-1</f>
-        <v>7.3373241799724154E-2</v>
+        <v>7.3925691557103823E-2</v>
       </c>
       <c r="Q72" s="288">
         <v>0.42913526059428814</v>
@@ -10961,12 +10958,11 @@
         <v>0.42555365398860762</v>
       </c>
       <c r="AG72" s="311">
-        <f t="shared" si="28"/>
-        <v>0.42232064731000413</v>
+        <v>0.42372433695680284</v>
       </c>
       <c r="AH72" s="302">
         <f>+AG72/AG71-1</f>
-        <v>9.5969846210482324E-2</v>
+        <v>9.961257960779113E-2</v>
       </c>
       <c r="AI72" s="288">
         <v>0.42391497681199863</v>
@@ -11319,23 +11315,23 @@
     </row>
     <row r="81" spans="1:37" ht="19.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="354"/>
-      <c r="C81" s="355"/>
-      <c r="D81" s="355"/>
-      <c r="E81" s="355"/>
-      <c r="F81" s="356"/>
-      <c r="G81" s="356"/>
-      <c r="H81" s="356"/>
-      <c r="I81" s="356"/>
-      <c r="J81" s="356"/>
-      <c r="K81" s="355"/>
-      <c r="L81" s="355"/>
-      <c r="M81" s="355"/>
-      <c r="N81" s="355"/>
-      <c r="O81" s="355"/>
-      <c r="P81" s="355"/>
-      <c r="Q81" s="355"/>
-      <c r="R81" s="355"/>
+      <c r="B81" s="355"/>
+      <c r="C81" s="356"/>
+      <c r="D81" s="356"/>
+      <c r="E81" s="356"/>
+      <c r="F81" s="357"/>
+      <c r="G81" s="357"/>
+      <c r="H81" s="357"/>
+      <c r="I81" s="357"/>
+      <c r="J81" s="357"/>
+      <c r="K81" s="356"/>
+      <c r="L81" s="356"/>
+      <c r="M81" s="356"/>
+      <c r="N81" s="356"/>
+      <c r="O81" s="356"/>
+      <c r="P81" s="356"/>
+      <c r="Q81" s="356"/>
+      <c r="R81" s="356"/>
       <c r="S81" s="7"/>
       <c r="T81" s="57"/>
       <c r="U81" s="56"/>
@@ -11362,13 +11358,13 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="69"/>
-      <c r="F82" s="348" t="s">
+      <c r="F82" s="349" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="349"/>
-      <c r="H82" s="349"/>
-      <c r="I82" s="349"/>
-      <c r="J82" s="350"/>
+      <c r="G82" s="350"/>
+      <c r="H82" s="350"/>
+      <c r="I82" s="350"/>
+      <c r="J82" s="351"/>
       <c r="K82" s="70"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -11547,7 +11543,7 @@
         <v>27.25</v>
       </c>
       <c r="O85" s="33">
-        <f t="shared" ref="O85:O105" si="31">AVERAGE(C85:N85)</f>
+        <f t="shared" ref="O85:O105" si="28">AVERAGE(C85:N85)</f>
         <v>21.26275</v>
       </c>
       <c r="P85" s="34"/>
@@ -11615,11 +11611,11 @@
         <v>29.238</v>
       </c>
       <c r="O86" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>28.221416666666666</v>
       </c>
       <c r="P86" s="41">
-        <f t="shared" ref="P86:P95" si="32">(O86/O85)-1</f>
+        <f t="shared" ref="P86:P95" si="29">(O86/O85)-1</f>
         <v>0.3272703044839762</v>
       </c>
       <c r="Q86" s="79"/>
@@ -11686,11 +11682,11 @@
         <v>26.564</v>
       </c>
       <c r="O87" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>28.694750000000003</v>
       </c>
       <c r="P87" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1.6772132275429286E-2</v>
       </c>
       <c r="Q87" s="79"/>
@@ -11757,11 +11753,11 @@
         <v>23.651</v>
       </c>
       <c r="O88" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>24.476749999999999</v>
       </c>
       <c r="P88" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-0.14699553054130121</v>
       </c>
       <c r="Q88" s="79"/>
@@ -11828,11 +11824,11 @@
         <v>24.449000000000002</v>
       </c>
       <c r="O89" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>24.073583333333335</v>
       </c>
       <c r="P89" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-1.6471413348041031E-2</v>
       </c>
       <c r="Q89" s="79"/>
@@ -11899,11 +11895,11 @@
         <v>21.692</v>
       </c>
       <c r="O90" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>23.466833333333337</v>
       </c>
       <c r="P90" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-2.5203975311804405E-2</v>
       </c>
       <c r="Q90" s="79"/>
@@ -11970,11 +11966,11 @@
         <v>24.353000000000002</v>
       </c>
       <c r="O91" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>20.947500000000002</v>
       </c>
       <c r="P91" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-0.10735719206539729</v>
       </c>
       <c r="Q91" s="79"/>
@@ -12041,11 +12037,11 @@
         <v>19.702999999999999</v>
       </c>
       <c r="O92" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>22.567833333333329</v>
       </c>
       <c r="P92" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>7.7352110434816934E-2</v>
       </c>
       <c r="Q92" s="79"/>
@@ -12112,11 +12108,11 @@
         <v>19.975000000000001</v>
       </c>
       <c r="O93" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>20.057583333333334</v>
       </c>
       <c r="P93" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-0.11123132482072551</v>
       </c>
       <c r="Q93" s="79"/>
@@ -12183,11 +12179,11 @@
         <v>19.97</v>
       </c>
       <c r="O94" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>19.313333333333336</v>
       </c>
       <c r="P94" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>-3.7105666601576215E-2</v>
       </c>
       <c r="Q94" s="79"/>
@@ -12254,11 +12250,11 @@
         <v>19.303999999999998</v>
       </c>
       <c r="O95" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>20.310083333333335</v>
       </c>
       <c r="P95" s="41">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>5.1609423541594701E-2</v>
       </c>
       <c r="Q95" s="79"/>
@@ -12325,11 +12321,11 @@
         <v>21.363</v>
       </c>
       <c r="O96" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>20.484500000000001</v>
       </c>
       <c r="P96" s="41">
-        <f t="shared" ref="P96:P105" si="33">O96/O95-1</f>
+        <f t="shared" ref="P96:P105" si="30">O96/O95-1</f>
         <v>8.5876883813869043E-3</v>
       </c>
       <c r="Q96" s="79"/>
@@ -12396,11 +12392,11 @@
         <v>24.106999999999999</v>
       </c>
       <c r="O97" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>23.246166666666664</v>
       </c>
       <c r="P97" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0.13481738224836648</v>
       </c>
       <c r="Q97" s="79"/>
@@ -12467,11 +12463,11 @@
         <v>29.78</v>
       </c>
       <c r="O98" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>27.326999999999998</v>
       </c>
       <c r="P98" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0.17554865676778264</v>
       </c>
       <c r="Q98" s="79"/>
@@ -12538,11 +12534,11 @@
         <v>28.84</v>
       </c>
       <c r="O99" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>30.155583333333336</v>
       </c>
       <c r="P99" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0.10350873982996078</v>
       </c>
       <c r="Q99" s="79"/>
@@ -12609,11 +12605,11 @@
         <v>28.88</v>
       </c>
       <c r="O100" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>28.674083333333332</v>
       </c>
       <c r="P100" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>-4.9128547228678099E-2</v>
       </c>
       <c r="Q100" s="79"/>
@@ -12680,11 +12676,11 @@
         <v>32.213999999999999</v>
       </c>
       <c r="O101" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>30.722083333333334</v>
       </c>
       <c r="P101" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>7.1423381741351877E-2</v>
       </c>
       <c r="Q101" s="79"/>
@@ -12751,11 +12747,11 @@
         <v>37.585000000000001</v>
       </c>
       <c r="O102" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>35.255249999999997</v>
       </c>
       <c r="P102" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0.1475540124503274</v>
       </c>
       <c r="Q102" s="79"/>
@@ -12822,11 +12818,11 @@
         <v>42.396000000000001</v>
       </c>
       <c r="O103" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>41.993583333333341</v>
       </c>
       <c r="P103" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0.19112992627575598</v>
       </c>
       <c r="Q103" s="79"/>
@@ -12893,11 +12889,11 @@
         <v>44.325000000000003</v>
       </c>
       <c r="O104" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>43.553166666666669</v>
       </c>
       <c r="P104" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>3.7138610462312593E-2</v>
       </c>
       <c r="Q104" s="79"/>
@@ -12964,11 +12960,11 @@
         <v>39.090000000000003</v>
       </c>
       <c r="O105" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>41.16758333333334</v>
       </c>
       <c r="P105" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>-5.4774050107339933E-2</v>
       </c>
       <c r="Q105" s="79"/>
@@ -13035,11 +13031,11 @@
         <v>39.302999999999997</v>
       </c>
       <c r="O106" s="40">
-        <f t="shared" ref="O106" si="34">AVERAGE(C106:N106)</f>
+        <f t="shared" ref="O106" si="31">AVERAGE(C106:N106)</f>
         <v>38.821337301587306</v>
       </c>
       <c r="P106" s="41">
-        <f t="shared" ref="P106" si="35">O106/O105-1</f>
+        <f t="shared" ref="P106" si="32">O106/O105-1</f>
         <v>-5.6992561665534569E-2</v>
       </c>
       <c r="Q106" s="79"/>
@@ -13106,11 +13102,11 @@
         <v>44.009</v>
       </c>
       <c r="O107" s="40">
-        <f t="shared" ref="O107" si="36">AVERAGE(C107:N107)</f>
+        <f t="shared" ref="O107" si="33">AVERAGE(C107:N107)</f>
         <v>40.213166666666673</v>
       </c>
       <c r="P107" s="41">
-        <f t="shared" ref="P107" si="37">O107/O106-1</f>
+        <f t="shared" ref="P107" si="34">O107/O106-1</f>
         <v>3.5852174649904756E-2</v>
       </c>
       <c r="Q107" s="79"/>
@@ -13177,11 +13173,11 @@
         <v>39.149000000000001</v>
       </c>
       <c r="O108" s="40">
-        <f t="shared" ref="O108" si="38">AVERAGE(C108:N108)</f>
+        <f t="shared" ref="O108" si="35">AVERAGE(C108:N108)</f>
         <v>41.081083333333325</v>
       </c>
       <c r="P108" s="41">
-        <f t="shared" ref="P108" si="39">O108/O107-1</f>
+        <f t="shared" ref="P108" si="36">O108/O107-1</f>
         <v>2.1582897807102652E-2</v>
       </c>
       <c r="Q108" s="79"/>
@@ -13664,7 +13660,7 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="O90:O105 O13:O34 O49:O72 O85:O89 AG20:AG33 AG12:AG19 AG49:AG72 AG34:AH34 O106:O108 O35:P35 S35:T35 AG35 O36 AG36:AH36" formulaRange="1"/>
+    <ignoredError sqref="O90:O105 O13:O34 O49:O71 O85:O89 AG20:AG33 AG12:AG19 AG49:AG71 AG34:AH34 O106:O108 O35:P35 S35:T35 AG35 AH36" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -13870,13 +13866,13 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="69"/>
-      <c r="F10" s="357" t="s">
+      <c r="F10" s="358" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="358"/>
-      <c r="H10" s="358"/>
-      <c r="I10" s="358"/>
-      <c r="J10" s="359"/>
+      <c r="G10" s="359"/>
+      <c r="H10" s="359"/>
+      <c r="I10" s="359"/>
+      <c r="J10" s="360"/>
       <c r="K10" s="70"/>
       <c r="L10" s="12" t="s">
         <v>2</v>
@@ -13913,11 +13909,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="360" t="s">
+      <c r="G12" s="361" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="361"/>
-      <c r="I12" s="362"/>
+      <c r="H12" s="362"/>
+      <c r="I12" s="363"/>
       <c r="J12" s="70"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -14788,11 +14784,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="363" t="s">
+      <c r="G33" s="364" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="364"/>
-      <c r="I33" s="365"/>
+      <c r="H33" s="365"/>
+      <c r="I33" s="366"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -15659,13 +15655,13 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="69"/>
-      <c r="F54" s="366" t="s">
+      <c r="F54" s="367" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="367"/>
-      <c r="H54" s="367"/>
-      <c r="I54" s="367"/>
-      <c r="J54" s="367"/>
+      <c r="G54" s="368"/>
+      <c r="H54" s="368"/>
+      <c r="I54" s="368"/>
+      <c r="J54" s="368"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -16429,11 +16425,11 @@
         <v>220.09609094318526</v>
       </c>
       <c r="O70" s="120">
-        <v>225.82868299028016</v>
+        <v>225.78132986254749</v>
       </c>
       <c r="P70" s="41">
         <f t="shared" si="2"/>
-        <v>8.2072956193296465E-2</v>
+        <v>8.1846060573872892E-2</v>
       </c>
       <c r="Q70" s="90"/>
     </row>
@@ -16775,17 +16771,17 @@
     <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="131"/>
-      <c r="C5" s="345" t="s">
+      <c r="C5" s="346" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="346"/>
-      <c r="E5" s="346"/>
-      <c r="F5" s="346"/>
-      <c r="G5" s="346"/>
-      <c r="H5" s="346"/>
-      <c r="I5" s="346"/>
-      <c r="J5" s="346"/>
-      <c r="K5" s="347"/>
+      <c r="D5" s="347"/>
+      <c r="E5" s="347"/>
+      <c r="F5" s="347"/>
+      <c r="G5" s="347"/>
+      <c r="H5" s="347"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="347"/>
+      <c r="K5" s="348"/>
       <c r="L5" s="70"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -29862,7 +29858,7 @@
       <c r="D295" s="251">
         <v>6.7370038160060441E-3</v>
       </c>
-      <c r="E295" s="368">
+      <c r="E295" s="345">
         <v>16.66</v>
       </c>
       <c r="F295" s="253">
@@ -30335,14 +30331,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30587,21 +30581,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30626,9 +30619,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data_raw/precio_leche_productor.xlsx
+++ b/data_raw/precio_leche_productor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/1- Producción y precios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1234" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D32E48E1-1C71-42DE-84CB-53937A08B4A4}"/>
+  <xr:revisionPtr revIDLastSave="1311" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827EC136-D3C3-4E04-A771-6B3C29952959}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Precio en tambo" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="111">
   <si>
     <t>En los cuadros 1 y 2 se presentan los valores pagados en promedio incluyendo reliquidaciones efectuadas en  otros meses correspondientes al mes presentado.</t>
   </si>
@@ -2260,7 +2260,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="369">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2882,14 +2882,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="12" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2899,15 +2892,39 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="42" borderId="54" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="42" borderId="53" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="42" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="74" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="76" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2964,6 +2981,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4789,17 +4815,17 @@
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="352" t="s">
+      <c r="E10" s="359" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="353"/>
-      <c r="G10" s="353"/>
-      <c r="H10" s="353"/>
-      <c r="I10" s="353"/>
-      <c r="J10" s="353"/>
-      <c r="K10" s="353"/>
-      <c r="L10" s="353"/>
-      <c r="M10" s="354"/>
+      <c r="F10" s="360"/>
+      <c r="G10" s="360"/>
+      <c r="H10" s="360"/>
+      <c r="I10" s="360"/>
+      <c r="J10" s="360"/>
+      <c r="K10" s="360"/>
+      <c r="L10" s="360"/>
+      <c r="M10" s="361"/>
       <c r="N10" s="17"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -4809,17 +4835,17 @@
       <c r="T10" s="19"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="349" t="s">
+      <c r="W10" s="356" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="350"/>
-      <c r="Y10" s="350"/>
-      <c r="Z10" s="350"/>
-      <c r="AA10" s="350"/>
-      <c r="AB10" s="350"/>
-      <c r="AC10" s="350"/>
-      <c r="AD10" s="350"/>
-      <c r="AE10" s="351"/>
+      <c r="X10" s="357"/>
+      <c r="Y10" s="357"/>
+      <c r="Z10" s="357"/>
+      <c r="AA10" s="357"/>
+      <c r="AB10" s="357"/>
+      <c r="AC10" s="357"/>
+      <c r="AD10" s="357"/>
+      <c r="AE10" s="358"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
@@ -7611,22 +7637,22 @@
         <v>17.823437113366513</v>
       </c>
       <c r="I36" s="216">
-        <v>17.60667227152063</v>
+        <v>17.57</v>
       </c>
       <c r="J36" s="216">
-        <v>17.360172130174671</v>
+        <v>17.34</v>
       </c>
       <c r="K36" s="216">
-        <v>17.379344958474494</v>
+        <v>17.36</v>
       </c>
       <c r="L36" s="216">
-        <v>17.028347887022893</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="M36" s="216">
-        <v>16.817321827093544</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="N36" s="216">
-        <v>16.666737003816007</v>
+        <v>16.66</v>
       </c>
       <c r="O36" s="311">
         <v>17.531654337842706</v>
@@ -7703,17 +7729,21 @@
       <c r="B37" s="294">
         <v>2026</v>
       </c>
-      <c r="C37" s="339">
+      <c r="C37" s="354">
         <v>16.087724443768948</v>
       </c>
-      <c r="D37" s="340">
+      <c r="D37" s="355">
         <v>16.511849716258542</v>
       </c>
-      <c r="E37" s="340">
+      <c r="E37" s="355">
         <v>16.88282948579424</v>
       </c>
-      <c r="F37" s="303"/>
-      <c r="G37" s="303"/>
+      <c r="F37" s="339">
+        <v>16.688703974646522</v>
+      </c>
+      <c r="G37" s="339">
+        <v>17.1396984105765</v>
+      </c>
       <c r="H37" s="303"/>
       <c r="I37" s="303"/>
       <c r="J37" s="303"/>
@@ -7729,17 +7759,21 @@
       <c r="T37" s="294">
         <v>2026</v>
       </c>
-      <c r="U37" s="339">
-        <v>16.087724443768948</v>
-      </c>
-      <c r="V37" s="341">
-        <v>16.511849716258542</v>
-      </c>
-      <c r="W37" s="341">
-        <v>16.88282948579424</v>
-      </c>
-      <c r="X37" s="303"/>
-      <c r="Y37" s="303"/>
+      <c r="U37" s="354">
+        <v>16.03</v>
+      </c>
+      <c r="V37" s="353">
+        <v>16.38</v>
+      </c>
+      <c r="W37" s="353">
+        <v>16.79</v>
+      </c>
+      <c r="X37" s="339">
+        <v>16.688703974646522</v>
+      </c>
+      <c r="Y37" s="339">
+        <v>17.1396984105765</v>
+      </c>
       <c r="Z37" s="303"/>
       <c r="AA37" s="303"/>
       <c r="AB37" s="303"/>
@@ -8018,21 +8052,11 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="7">
-        <v>16.666737003816007</v>
-      </c>
-      <c r="U44" s="7">
-        <v>6.7370038160060441E-3</v>
-      </c>
-      <c r="V44" s="7">
-        <v>16.66</v>
-      </c>
-      <c r="W44" s="7">
-        <v>0.42572574021854981</v>
-      </c>
-      <c r="X44" s="7">
-        <v>0.42555365398860762</v>
-      </c>
+      <c r="T44" s="7"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7"/>
@@ -8049,23 +8073,23 @@
     </row>
     <row r="45" spans="1:37" ht="36" customHeight="1">
       <c r="A45" s="68"/>
-      <c r="B45" s="355"/>
-      <c r="C45" s="356"/>
-      <c r="D45" s="356"/>
-      <c r="E45" s="357"/>
-      <c r="F45" s="357"/>
-      <c r="G45" s="357"/>
-      <c r="H45" s="357"/>
-      <c r="I45" s="357"/>
-      <c r="J45" s="357"/>
-      <c r="K45" s="357"/>
-      <c r="L45" s="357"/>
-      <c r="M45" s="357"/>
-      <c r="N45" s="356"/>
-      <c r="O45" s="356"/>
-      <c r="P45" s="356"/>
-      <c r="Q45" s="356"/>
-      <c r="R45" s="356"/>
+      <c r="B45" s="362"/>
+      <c r="C45" s="363"/>
+      <c r="D45" s="363"/>
+      <c r="E45" s="364"/>
+      <c r="F45" s="364"/>
+      <c r="G45" s="364"/>
+      <c r="H45" s="364"/>
+      <c r="I45" s="364"/>
+      <c r="J45" s="364"/>
+      <c r="K45" s="364"/>
+      <c r="L45" s="364"/>
+      <c r="M45" s="364"/>
+      <c r="N45" s="363"/>
+      <c r="O45" s="363"/>
+      <c r="P45" s="363"/>
+      <c r="Q45" s="363"/>
+      <c r="R45" s="363"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
@@ -8091,17 +8115,17 @@
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="69"/>
-      <c r="E46" s="352" t="s">
+      <c r="E46" s="359" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="353"/>
-      <c r="G46" s="353"/>
-      <c r="H46" s="353"/>
-      <c r="I46" s="353"/>
-      <c r="J46" s="353"/>
-      <c r="K46" s="353"/>
-      <c r="L46" s="353"/>
-      <c r="M46" s="354"/>
+      <c r="F46" s="360"/>
+      <c r="G46" s="360"/>
+      <c r="H46" s="360"/>
+      <c r="I46" s="360"/>
+      <c r="J46" s="360"/>
+      <c r="K46" s="360"/>
+      <c r="L46" s="360"/>
+      <c r="M46" s="361"/>
       <c r="N46" s="70"/>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -8111,17 +8135,17 @@
       <c r="T46" s="71"/>
       <c r="U46" s="7"/>
       <c r="V46" s="69"/>
-      <c r="W46" s="349" t="s">
+      <c r="W46" s="356" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="350"/>
-      <c r="Y46" s="350"/>
-      <c r="Z46" s="350"/>
-      <c r="AA46" s="350"/>
-      <c r="AB46" s="350"/>
-      <c r="AC46" s="350"/>
-      <c r="AD46" s="350"/>
-      <c r="AE46" s="351"/>
+      <c r="X46" s="357"/>
+      <c r="Y46" s="357"/>
+      <c r="Z46" s="357"/>
+      <c r="AA46" s="357"/>
+      <c r="AB46" s="357"/>
+      <c r="AC46" s="357"/>
+      <c r="AD46" s="357"/>
+      <c r="AE46" s="358"/>
       <c r="AF46" s="70"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="7"/>
@@ -10886,22 +10910,22 @@
         <v>0.43627153065468532</v>
       </c>
       <c r="I72" s="216">
-        <v>0.43747632737466152</v>
+        <v>0.43656512448442081</v>
       </c>
       <c r="J72" s="216">
-        <v>0.43353824963600807</v>
+        <v>0.4330344879254801</v>
       </c>
       <c r="K72" s="216">
-        <v>0.43480973126030759</v>
+        <v>0.43432574430823118</v>
       </c>
       <c r="L72" s="216">
-        <v>0.42652976697700301</v>
+        <v>0.42607018510632971</v>
       </c>
       <c r="M72" s="216">
-        <v>0.42335418958547844</v>
+        <v>0.42316987211761153</v>
       </c>
       <c r="N72" s="216">
-        <v>0.42572574021854981</v>
+        <v>0.42555365398860762</v>
       </c>
       <c r="O72" s="311">
         <v>0.42911807488608505</v>
@@ -10978,17 +11002,21 @@
       <c r="B73" s="294">
         <v>2026</v>
       </c>
-      <c r="C73" s="342">
-        <v>0.41852609182780376</v>
-      </c>
-      <c r="D73" s="341">
-        <v>0.42813414878674882</v>
-      </c>
-      <c r="E73" s="341">
-        <v>0.4193658275571126</v>
-      </c>
-      <c r="F73" s="303"/>
-      <c r="G73" s="303"/>
+      <c r="C73" s="352">
+        <v>0.41702437628450273</v>
+      </c>
+      <c r="D73" s="353">
+        <v>0.42471543029014441</v>
+      </c>
+      <c r="E73" s="353">
+        <v>0.41705996323712052</v>
+      </c>
+      <c r="F73" s="339">
+        <v>0.41712374652319534</v>
+      </c>
+      <c r="G73" s="339">
+        <v>0.4284389054012373</v>
+      </c>
       <c r="H73" s="303"/>
       <c r="I73" s="303"/>
       <c r="J73" s="303"/>
@@ -11004,17 +11032,21 @@
       <c r="T73" s="294">
         <v>2026</v>
       </c>
-      <c r="U73" s="342">
-        <v>0.41852609182780376</v>
-      </c>
-      <c r="V73" s="341">
-        <v>0.42813414878674882</v>
-      </c>
-      <c r="W73" s="341">
-        <v>0.4193658275571126</v>
-      </c>
-      <c r="X73" s="303"/>
-      <c r="Y73" s="303"/>
+      <c r="U73" s="352">
+        <v>0.41702437628450273</v>
+      </c>
+      <c r="V73" s="353">
+        <v>0.42471543029014441</v>
+      </c>
+      <c r="W73" s="353">
+        <v>0.41705996323712052</v>
+      </c>
+      <c r="X73" s="339">
+        <v>0.41712374652319534</v>
+      </c>
+      <c r="Y73" s="339">
+        <v>0.4284389054012373</v>
+      </c>
       <c r="Z73" s="303"/>
       <c r="AA73" s="303"/>
       <c r="AB73" s="303"/>
@@ -11315,23 +11347,23 @@
     </row>
     <row r="81" spans="1:37" ht="19.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="355"/>
-      <c r="C81" s="356"/>
-      <c r="D81" s="356"/>
-      <c r="E81" s="356"/>
-      <c r="F81" s="357"/>
-      <c r="G81" s="357"/>
-      <c r="H81" s="357"/>
-      <c r="I81" s="357"/>
-      <c r="J81" s="357"/>
-      <c r="K81" s="356"/>
-      <c r="L81" s="356"/>
-      <c r="M81" s="356"/>
-      <c r="N81" s="356"/>
-      <c r="O81" s="356"/>
-      <c r="P81" s="356"/>
-      <c r="Q81" s="356"/>
-      <c r="R81" s="356"/>
+      <c r="B81" s="362"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="364"/>
+      <c r="G81" s="364"/>
+      <c r="H81" s="364"/>
+      <c r="I81" s="364"/>
+      <c r="J81" s="364"/>
+      <c r="K81" s="363"/>
+      <c r="L81" s="363"/>
+      <c r="M81" s="363"/>
+      <c r="N81" s="363"/>
+      <c r="O81" s="363"/>
+      <c r="P81" s="363"/>
+      <c r="Q81" s="363"/>
+      <c r="R81" s="363"/>
       <c r="S81" s="7"/>
       <c r="T81" s="57"/>
       <c r="U81" s="56"/>
@@ -11358,13 +11390,13 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="69"/>
-      <c r="F82" s="349" t="s">
+      <c r="F82" s="356" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="350"/>
-      <c r="H82" s="350"/>
-      <c r="I82" s="350"/>
-      <c r="J82" s="351"/>
+      <c r="G82" s="357"/>
+      <c r="H82" s="357"/>
+      <c r="I82" s="357"/>
+      <c r="J82" s="358"/>
       <c r="K82" s="70"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -13216,8 +13248,12 @@
       <c r="E109" s="46">
         <v>40.258000000000003</v>
       </c>
-      <c r="F109" s="46"/>
-      <c r="G109" s="46"/>
+      <c r="F109" s="46">
+        <v>40.009</v>
+      </c>
+      <c r="G109" s="46">
+        <v>40.005000000000003</v>
+      </c>
       <c r="H109" s="46"/>
       <c r="I109" s="46"/>
       <c r="J109" s="46"/>
@@ -13866,13 +13902,13 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="69"/>
-      <c r="F10" s="358" t="s">
+      <c r="F10" s="365" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="359"/>
-      <c r="H10" s="359"/>
-      <c r="I10" s="359"/>
-      <c r="J10" s="360"/>
+      <c r="G10" s="366"/>
+      <c r="H10" s="366"/>
+      <c r="I10" s="366"/>
+      <c r="J10" s="367"/>
       <c r="K10" s="70"/>
       <c r="L10" s="12" t="s">
         <v>2</v>
@@ -13909,11 +13945,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="361" t="s">
+      <c r="G12" s="368" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="362"/>
-      <c r="I12" s="363"/>
+      <c r="H12" s="369"/>
+      <c r="I12" s="370"/>
       <c r="J12" s="70"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -14702,8 +14738,12 @@
       <c r="E29" s="104">
         <v>4.2062417938768498E-2</v>
       </c>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
+      <c r="F29" s="104">
+        <v>4.1966373257041917E-2</v>
+      </c>
+      <c r="G29" s="104">
+        <v>4.196503986612269E-2</v>
+      </c>
       <c r="H29" s="104"/>
       <c r="I29" s="104"/>
       <c r="J29" s="104"/>
@@ -14784,11 +14824,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="364" t="s">
+      <c r="G33" s="371" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="365"/>
-      <c r="I33" s="366"/>
+      <c r="H33" s="372"/>
+      <c r="I33" s="373"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -15575,8 +15615,12 @@
       <c r="E50" s="104">
         <v>3.6753182245234967E-2</v>
       </c>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
+      <c r="F50" s="104">
+        <v>3.6266723938049715E-2</v>
+      </c>
+      <c r="G50" s="104">
+        <v>3.7436375997092319E-2</v>
+      </c>
       <c r="H50" s="104"/>
       <c r="I50" s="104"/>
       <c r="J50" s="104"/>
@@ -15655,13 +15699,13 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="69"/>
-      <c r="F54" s="367" t="s">
+      <c r="F54" s="374" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="368"/>
-      <c r="H54" s="368"/>
-      <c r="I54" s="368"/>
-      <c r="J54" s="368"/>
+      <c r="G54" s="375"/>
+      <c r="H54" s="375"/>
+      <c r="I54" s="375"/>
+      <c r="J54" s="375"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -16388,7 +16432,7 @@
       <c r="B70" s="200">
         <v>2025</v>
       </c>
-      <c r="C70" s="343">
+      <c r="C70" s="340">
         <v>238.3837448020885</v>
       </c>
       <c r="D70" s="274">
@@ -16407,22 +16451,22 @@
         <v>223.81626618915374</v>
       </c>
       <c r="I70" s="215">
-        <v>225.16411186475963</v>
+        <v>224.69512605530818</v>
       </c>
       <c r="J70" s="215">
-        <v>225.7928630741242</v>
+        <v>225.53049683764399</v>
       </c>
       <c r="K70" s="215">
-        <v>225.16280902377707</v>
+        <v>224.91218017666156</v>
       </c>
       <c r="L70" s="215">
-        <v>222.70494094456652</v>
+        <v>222.46497843481507</v>
       </c>
       <c r="M70" s="215">
-        <v>221.9571258978051</v>
+        <v>221.86049150412978</v>
       </c>
       <c r="N70" s="215">
-        <v>220.09609094318526</v>
+        <v>220.00712402637166</v>
       </c>
       <c r="O70" s="120">
         <v>225.78132986254749</v>
@@ -16439,16 +16483,20 @@
         <v>2026</v>
       </c>
       <c r="C71" s="202">
-        <v>207.9518268033307</v>
+        <v>207.20567382346613</v>
       </c>
       <c r="D71" s="202">
-        <v>208.513142942049</v>
+        <v>206.8481327096693</v>
       </c>
       <c r="E71" s="202">
-        <v>207.96766820125683</v>
-      </c>
-      <c r="F71" s="202"/>
-      <c r="G71" s="202"/>
+        <v>206.82416724265303</v>
+      </c>
+      <c r="F71" s="202">
+        <v>207.10704035784963</v>
+      </c>
+      <c r="G71" s="202">
+        <v>209.57414566045259</v>
+      </c>
       <c r="H71" s="202"/>
       <c r="I71" s="202"/>
       <c r="J71" s="202"/>
@@ -16667,7 +16715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R321"/>
+  <dimension ref="A1:R322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
@@ -16771,17 +16819,17 @@
     <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="131"/>
-      <c r="C5" s="346" t="s">
+      <c r="C5" s="376" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="347"/>
-      <c r="E5" s="347"/>
-      <c r="F5" s="347"/>
-      <c r="G5" s="347"/>
-      <c r="H5" s="347"/>
-      <c r="I5" s="347"/>
-      <c r="J5" s="347"/>
-      <c r="K5" s="348"/>
+      <c r="D5" s="377"/>
+      <c r="E5" s="377"/>
+      <c r="F5" s="377"/>
+      <c r="G5" s="377"/>
+      <c r="H5" s="377"/>
+      <c r="I5" s="377"/>
+      <c r="J5" s="377"/>
+      <c r="K5" s="378"/>
       <c r="L5" s="70"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -27464,7 +27512,7 @@
       <c r="B242" s="148">
         <v>44378</v>
       </c>
-      <c r="C242" s="176">
+      <c r="C242" s="347">
         <f t="shared" si="16"/>
         <v>15.813504263244047</v>
       </c>
@@ -27510,7 +27558,7 @@
       <c r="B243" s="148">
         <v>44409</v>
       </c>
-      <c r="C243" s="176">
+      <c r="C243" s="347">
         <f t="shared" si="16"/>
         <v>15.836401931120198</v>
       </c>
@@ -27556,7 +27604,7 @@
       <c r="B244" s="148">
         <v>44440</v>
       </c>
-      <c r="C244" s="176">
+      <c r="C244" s="347">
         <f t="shared" si="16"/>
         <v>15.656062480787583</v>
       </c>
@@ -27735,7 +27783,7 @@
         <v>44562</v>
       </c>
       <c r="C248" s="208">
-        <f t="shared" ref="C248:C295" si="17">E248+D248</f>
+        <f t="shared" ref="C248:C289" si="17">E248+D248</f>
         <v>15.91</v>
       </c>
       <c r="D248" s="223">
@@ -28449,11 +28497,11 @@
         <v>17.61</v>
       </c>
       <c r="F264" s="203">
-        <f t="shared" ref="F264:F298" si="18">C264/H264</f>
+        <f t="shared" ref="F264:F300" si="18">C264/H264</f>
         <v>0.45315354725817658</v>
       </c>
       <c r="G264" s="204">
-        <f t="shared" ref="G264:G298" si="19">E264/H264</f>
+        <f t="shared" ref="G264:G300" si="19">E264/H264</f>
         <v>0.45315354725817658</v>
       </c>
       <c r="H264" s="205">
@@ -28570,7 +28618,7 @@
       <c r="B267" s="236">
         <v>45139</v>
       </c>
-      <c r="C267" s="210">
+      <c r="C267" s="346">
         <f t="shared" si="17"/>
         <v>14.422481272119411</v>
       </c>
@@ -28616,7 +28664,7 @@
       <c r="B268" s="236">
         <v>45170</v>
       </c>
-      <c r="C268" s="210">
+      <c r="C268" s="346">
         <f t="shared" si="17"/>
         <v>14.304367760737883</v>
       </c>
@@ -28662,7 +28710,7 @@
       <c r="B269" s="236">
         <v>45200</v>
       </c>
-      <c r="C269" s="210">
+      <c r="C269" s="346">
         <f t="shared" si="17"/>
         <v>14.58323079133924</v>
       </c>
@@ -28707,7 +28755,7 @@
       <c r="B270" s="236">
         <v>45231</v>
       </c>
-      <c r="C270" s="210">
+      <c r="C270" s="346">
         <f t="shared" si="17"/>
         <v>14.402061302575852</v>
       </c>
@@ -28735,7 +28783,7 @@
         <v>3.4547912831612973E-2</v>
       </c>
       <c r="K270" s="238">
-        <f t="shared" ref="K270:K298" si="21">C270/1.03/(I270+J270)</f>
+        <f t="shared" ref="K270:K300" si="21">C270/1.03/(I270+J270)</f>
         <v>192.128050061945</v>
       </c>
       <c r="L270" s="241" t="s">
@@ -28841,7 +28889,7 @@
       <c r="B273" s="236">
         <v>45323</v>
       </c>
-      <c r="C273" s="249">
+      <c r="C273" s="343">
         <f t="shared" si="17"/>
         <v>15.434719101666696</v>
       </c>
@@ -28888,7 +28936,7 @@
       <c r="B274" s="236">
         <v>45352</v>
       </c>
-      <c r="C274" s="249">
+      <c r="C274" s="343">
         <f t="shared" si="17"/>
         <v>16.136467771275814</v>
       </c>
@@ -28935,7 +28983,7 @@
       <c r="B275" s="236">
         <v>45383</v>
       </c>
-      <c r="C275" s="249">
+      <c r="C275" s="343">
         <f t="shared" si="17"/>
         <v>16.291173494065244</v>
       </c>
@@ -28981,7 +29029,7 @@
       <c r="B276" s="236">
         <v>45413</v>
       </c>
-      <c r="C276" s="249">
+      <c r="C276" s="343">
         <f t="shared" si="17"/>
         <v>16.307808885434902</v>
       </c>
@@ -29028,7 +29076,7 @@
         <v>45444</v>
       </c>
       <c r="C277" s="249">
-        <f t="shared" si="17"/>
+        <f>E277</f>
         <v>15.35</v>
       </c>
       <c r="D277" s="225">
@@ -29071,7 +29119,7 @@
       <c r="B278" s="236">
         <v>45474</v>
       </c>
-      <c r="C278" s="249">
+      <c r="C278" s="343">
         <f t="shared" si="17"/>
         <v>16.048750103626539</v>
       </c>
@@ -29117,7 +29165,7 @@
       <c r="B279" s="236">
         <v>45505</v>
       </c>
-      <c r="C279" s="249">
+      <c r="C279" s="343">
         <f t="shared" si="17"/>
         <v>16.257094942730532</v>
       </c>
@@ -29164,7 +29212,7 @@
       <c r="B280" s="236">
         <v>45536</v>
       </c>
-      <c r="C280" s="249">
+      <c r="C280" s="343">
         <f t="shared" si="17"/>
         <v>16.555598977904481</v>
       </c>
@@ -29211,7 +29259,7 @@
       <c r="B281" s="236">
         <v>45566</v>
       </c>
-      <c r="C281" s="249">
+      <c r="C281" s="343">
         <f t="shared" si="17"/>
         <v>16.268556828232569</v>
       </c>
@@ -29258,7 +29306,7 @@
       <c r="B282" s="236">
         <v>45597</v>
       </c>
-      <c r="C282" s="225">
+      <c r="C282" s="344">
         <f t="shared" si="17"/>
         <v>16.591860867115837</v>
       </c>
@@ -29305,7 +29353,7 @@
       <c r="B283" s="236">
         <v>45627</v>
       </c>
-      <c r="C283" s="225">
+      <c r="C283" s="344">
         <f t="shared" si="17"/>
         <v>17.254154066110118</v>
       </c>
@@ -29352,7 +29400,7 @@
       <c r="B284" s="226">
         <v>45658</v>
       </c>
-      <c r="C284" s="228">
+      <c r="C284" s="345">
         <f t="shared" si="17"/>
         <v>18.134875224364666</v>
       </c>
@@ -29399,7 +29447,7 @@
       <c r="B285" s="236">
         <v>45689</v>
       </c>
-      <c r="C285" s="225">
+      <c r="C285" s="344">
         <f t="shared" si="17"/>
         <v>18.055108499168696</v>
       </c>
@@ -29446,7 +29494,7 @@
       <c r="B286" s="236">
         <v>45717</v>
       </c>
-      <c r="C286" s="225">
+      <c r="C286" s="344">
         <f t="shared" si="17"/>
         <v>18.381820583265164</v>
       </c>
@@ -29493,7 +29541,7 @@
       <c r="B287" s="236">
         <v>45748</v>
       </c>
-      <c r="C287" s="225">
+      <c r="C287" s="344">
         <f t="shared" si="17"/>
         <v>18.21962865654822</v>
       </c>
@@ -29540,7 +29588,7 @@
       <c r="B288" s="236">
         <v>45778</v>
       </c>
-      <c r="C288" s="225">
+      <c r="C288" s="344">
         <f t="shared" si="17"/>
         <v>17.910545122656139</v>
       </c>
@@ -29632,8 +29680,8 @@
         <v>45839</v>
       </c>
       <c r="C290" s="225">
-        <f t="shared" si="17"/>
-        <v>17.60667227152063</v>
+        <f>E290</f>
+        <v>17.57</v>
       </c>
       <c r="D290" s="225">
         <v>3.6672271520630607E-2</v>
@@ -29643,7 +29691,7 @@
       </c>
       <c r="F290" s="203">
         <f t="shared" si="18"/>
-        <v>0.43747632737466152</v>
+        <v>0.43656512448442081</v>
       </c>
       <c r="G290" s="204">
         <f t="shared" si="19"/>
@@ -29660,7 +29708,7 @@
       </c>
       <c r="K290" s="238">
         <f t="shared" si="21"/>
-        <v>225.16411186475963</v>
+        <v>224.69512605530818</v>
       </c>
       <c r="L290" s="263"/>
       <c r="M290" s="196"/>
@@ -29676,8 +29724,8 @@
         <v>45870</v>
       </c>
       <c r="C291" s="225">
-        <f t="shared" si="17"/>
-        <v>17.360172130174671</v>
+        <f t="shared" ref="C291:C295" si="22">E291</f>
+        <v>17.34</v>
       </c>
       <c r="D291" s="225">
         <v>2.0172130174670733E-2</v>
@@ -29687,7 +29735,7 @@
       </c>
       <c r="F291" s="203">
         <f t="shared" si="18"/>
-        <v>0.43353824963600807</v>
+        <v>0.4330344879254801</v>
       </c>
       <c r="G291" s="204">
         <f t="shared" si="19"/>
@@ -29704,7 +29752,7 @@
       </c>
       <c r="K291" s="238">
         <f t="shared" si="21"/>
-        <v>225.7928630741242</v>
+        <v>225.53049683764399</v>
       </c>
       <c r="L291" s="263"/>
       <c r="M291" s="196"/>
@@ -29720,8 +29768,8 @@
         <v>45901</v>
       </c>
       <c r="C292" s="225">
-        <f t="shared" si="17"/>
-        <v>17.379344958474494</v>
+        <f t="shared" si="22"/>
+        <v>17.36</v>
       </c>
       <c r="D292" s="225">
         <v>1.9344958474494831E-2</v>
@@ -29731,7 +29779,7 @@
       </c>
       <c r="F292" s="203">
         <f t="shared" si="18"/>
-        <v>0.43480973126030759</v>
+        <v>0.43432574430823118</v>
       </c>
       <c r="G292" s="204">
         <f t="shared" si="19"/>
@@ -29748,7 +29796,7 @@
       </c>
       <c r="K292" s="238">
         <f t="shared" si="21"/>
-        <v>225.16280902377707</v>
+        <v>224.91218017666156</v>
       </c>
       <c r="L292" s="263"/>
       <c r="M292" s="196"/>
@@ -29764,8 +29812,8 @@
         <v>45931</v>
       </c>
       <c r="C293" s="225">
-        <f t="shared" si="17"/>
-        <v>17.028347887022893</v>
+        <f t="shared" si="22"/>
+        <v>17.010000000000002</v>
       </c>
       <c r="D293" s="225">
         <v>1.8347887022889656E-2</v>
@@ -29775,7 +29823,7 @@
       </c>
       <c r="F293" s="203">
         <f t="shared" si="18"/>
-        <v>0.42652976697700301</v>
+        <v>0.42607018510632971</v>
       </c>
       <c r="G293" s="204">
         <f t="shared" si="19"/>
@@ -29792,7 +29840,7 @@
       </c>
       <c r="K293" s="238">
         <f t="shared" si="21"/>
-        <v>222.70494094456652</v>
+        <v>222.46497843481507</v>
       </c>
       <c r="L293" s="263"/>
       <c r="M293" s="196"/>
@@ -29808,8 +29856,8 @@
         <v>45962</v>
       </c>
       <c r="C294" s="225">
-        <f t="shared" si="17"/>
-        <v>16.817321827093544</v>
+        <f t="shared" si="22"/>
+        <v>16.809999999999999</v>
       </c>
       <c r="D294" s="225">
         <v>7.3218270935459214E-3</v>
@@ -29819,7 +29867,7 @@
       </c>
       <c r="F294" s="203">
         <f t="shared" si="18"/>
-        <v>0.42335418958547844</v>
+        <v>0.42316987211761153</v>
       </c>
       <c r="G294" s="204">
         <f t="shared" si="19"/>
@@ -29836,7 +29884,7 @@
       </c>
       <c r="K294" s="238">
         <f t="shared" si="21"/>
-        <v>221.9571258978051</v>
+        <v>221.86049150412978</v>
       </c>
       <c r="L294" s="263"/>
       <c r="M294" s="196"/>
@@ -29852,18 +29900,18 @@
         <v>45992</v>
       </c>
       <c r="C295" s="251">
-        <f t="shared" si="17"/>
-        <v>16.666737003816007</v>
+        <f t="shared" si="22"/>
+        <v>16.66</v>
       </c>
       <c r="D295" s="251">
         <v>6.7370038160060441E-3</v>
       </c>
-      <c r="E295" s="345">
+      <c r="E295" s="342">
         <v>16.66</v>
       </c>
       <c r="F295" s="253">
         <f t="shared" si="18"/>
-        <v>0.42572574021854981</v>
+        <v>0.42555365398860762</v>
       </c>
       <c r="G295" s="254">
         <f t="shared" si="19"/>
@@ -29880,7 +29928,7 @@
       </c>
       <c r="K295" s="258">
         <f t="shared" si="21"/>
-        <v>220.09609094318526</v>
+        <v>220.00712402637166</v>
       </c>
       <c r="L295" s="338"/>
       <c r="M295" s="196"/>
@@ -29895,35 +29943,36 @@
       <c r="B296" s="236">
         <v>46023</v>
       </c>
-      <c r="C296" s="277">
-        <v>16.087724443768948</v>
-      </c>
-      <c r="D296" s="277">
+      <c r="C296" s="225">
+        <f>E296</f>
+        <v>16.03</v>
+      </c>
+      <c r="D296" s="225">
         <v>7.1333961988045451E-3</v>
       </c>
-      <c r="E296" s="276">
-        <v>16.087724443768948</v>
-      </c>
-      <c r="F296" s="278">
+      <c r="E296" s="249">
+        <v>16.03</v>
+      </c>
+      <c r="F296" s="203">
         <f t="shared" si="18"/>
-        <v>0.41852609182780376</v>
-      </c>
-      <c r="G296" s="279">
+        <v>0.41702437628450273</v>
+      </c>
+      <c r="G296" s="204">
         <f t="shared" si="19"/>
-        <v>0.41852609182780376</v>
-      </c>
-      <c r="H296" s="280">
+        <v>0.41702437628450273</v>
+      </c>
+      <c r="H296" s="205">
         <v>38.439</v>
       </c>
-      <c r="I296" s="281">
+      <c r="I296" s="206">
         <v>3.9941008548791256E-2</v>
       </c>
-      <c r="J296" s="282">
+      <c r="J296" s="207">
         <v>3.516845399119628E-2</v>
       </c>
-      <c r="K296" s="283">
+      <c r="K296" s="238">
         <f t="shared" si="21"/>
-        <v>207.9518268033307</v>
+        <v>207.20567382346613</v>
       </c>
       <c r="L296" s="263"/>
       <c r="M296" s="196"/>
@@ -29938,35 +29987,36 @@
       <c r="B297" s="236">
         <v>46054</v>
       </c>
-      <c r="C297" s="277">
-        <v>16.511849716258542</v>
-      </c>
-      <c r="D297" s="277">
+      <c r="C297" s="225">
+        <f t="shared" ref="C297:C298" si="23">E297</f>
+        <v>16.38</v>
+      </c>
+      <c r="D297" s="225">
         <v>7.4405289607902729E-3</v>
       </c>
-      <c r="E297" s="276">
-        <v>16.511849716258542</v>
-      </c>
-      <c r="F297" s="278">
+      <c r="E297" s="249">
+        <v>16.38</v>
+      </c>
+      <c r="F297" s="203">
         <f t="shared" si="18"/>
-        <v>0.42813414878674882</v>
-      </c>
-      <c r="G297" s="279">
+        <v>0.42471543029014441</v>
+      </c>
+      <c r="G297" s="204">
         <f t="shared" si="19"/>
-        <v>0.42813414878674882</v>
-      </c>
-      <c r="H297" s="280">
+        <v>0.42471543029014441</v>
+      </c>
+      <c r="H297" s="205">
         <v>38.567</v>
       </c>
-      <c r="I297" s="281">
+      <c r="I297" s="206">
         <v>4.0747026305396547E-2</v>
       </c>
-      <c r="J297" s="282">
+      <c r="J297" s="207">
         <v>3.6135043709131683E-2</v>
       </c>
-      <c r="K297" s="283">
+      <c r="K297" s="238">
         <f t="shared" si="21"/>
-        <v>208.51314294204897</v>
+        <v>206.8481327096693</v>
       </c>
       <c r="L297" s="263"/>
       <c r="M297" s="196"/>
@@ -29978,40 +30028,41 @@
     </row>
     <row r="298" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A298" s="195"/>
-      <c r="B298" s="329">
+      <c r="B298" s="236">
         <v>46082</v>
       </c>
-      <c r="C298" s="330">
-        <v>16.88282948579424</v>
-      </c>
-      <c r="D298" s="330">
+      <c r="C298" s="225">
+        <f t="shared" si="23"/>
+        <v>16.79</v>
+      </c>
+      <c r="D298" s="225">
         <v>8.3954864794532329E-3</v>
       </c>
-      <c r="E298" s="331">
-        <v>16.88282948579424</v>
-      </c>
-      <c r="F298" s="332">
+      <c r="E298" s="249">
+        <v>16.79</v>
+      </c>
+      <c r="F298" s="203">
         <f t="shared" si="18"/>
-        <v>0.4193658275571126</v>
-      </c>
-      <c r="G298" s="333">
+        <v>0.41705996323712052</v>
+      </c>
+      <c r="G298" s="204">
         <f t="shared" si="19"/>
-        <v>0.4193658275571126</v>
-      </c>
-      <c r="H298" s="334">
+        <v>0.41705996323712052</v>
+      </c>
+      <c r="H298" s="205">
         <v>40.258000000000003</v>
       </c>
-      <c r="I298" s="335">
+      <c r="I298" s="206">
         <v>4.2062417938768498E-2</v>
       </c>
-      <c r="J298" s="336">
+      <c r="J298" s="207">
         <v>3.6753182245234967E-2</v>
       </c>
-      <c r="K298" s="337">
+      <c r="K298" s="238">
         <f t="shared" si="21"/>
-        <v>207.9676682012568</v>
-      </c>
-      <c r="L298" s="338"/>
+        <v>206.82416724265303</v>
+      </c>
+      <c r="L298" s="263"/>
       <c r="M298" s="196"/>
       <c r="N298" s="196"/>
       <c r="O298" s="197"/>
@@ -30020,18 +30071,41 @@
       <c r="R298" s="198"/>
     </row>
     <row r="299" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A299" s="344"/>
-      <c r="B299" s="344"/>
-      <c r="C299" s="344"/>
-      <c r="D299" s="344"/>
-      <c r="E299" s="344"/>
-      <c r="F299" s="344"/>
-      <c r="G299" s="344"/>
-      <c r="H299" s="344"/>
-      <c r="I299" s="344"/>
-      <c r="J299" s="344"/>
-      <c r="K299" s="344"/>
-      <c r="L299" s="344"/>
+      <c r="A299" s="196"/>
+      <c r="B299" s="348">
+        <v>46113</v>
+      </c>
+      <c r="C299" s="277">
+        <v>16.688703974646522</v>
+      </c>
+      <c r="D299" s="277">
+        <v>7.2386235954015445E-3</v>
+      </c>
+      <c r="E299" s="276">
+        <v>16.688703974646522</v>
+      </c>
+      <c r="F299" s="278">
+        <f t="shared" si="18"/>
+        <v>0.41712374652319534</v>
+      </c>
+      <c r="G299" s="279">
+        <f t="shared" si="19"/>
+        <v>0.41712374652319534</v>
+      </c>
+      <c r="H299" s="280">
+        <v>40.009</v>
+      </c>
+      <c r="I299" s="281">
+        <v>4.1966373257041917E-2</v>
+      </c>
+      <c r="J299" s="282">
+        <v>3.6266723938049715E-2</v>
+      </c>
+      <c r="K299" s="283">
+        <f t="shared" si="21"/>
+        <v>207.10704035784963</v>
+      </c>
+      <c r="L299" s="349"/>
       <c r="M299" s="196"/>
       <c r="N299" s="196"/>
       <c r="O299" s="197"/>
@@ -30040,18 +30114,41 @@
       <c r="R299" s="198"/>
     </row>
     <row r="300" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A300" s="344"/>
-      <c r="B300" s="344"/>
-      <c r="C300" s="344"/>
-      <c r="D300" s="344"/>
-      <c r="E300" s="344"/>
-      <c r="F300" s="344"/>
-      <c r="G300" s="344"/>
-      <c r="H300" s="344"/>
-      <c r="I300" s="344"/>
-      <c r="J300" s="344"/>
-      <c r="K300" s="344"/>
-      <c r="L300" s="260"/>
+      <c r="A300" s="341"/>
+      <c r="B300" s="350">
+        <v>46143</v>
+      </c>
+      <c r="C300" s="330">
+        <v>17.1396984105765</v>
+      </c>
+      <c r="D300" s="330">
+        <v>7.9065318674885494E-3</v>
+      </c>
+      <c r="E300" s="331">
+        <v>17.1396984105765</v>
+      </c>
+      <c r="F300" s="332">
+        <f t="shared" si="18"/>
+        <v>0.4284389054012373</v>
+      </c>
+      <c r="G300" s="333">
+        <f t="shared" si="19"/>
+        <v>0.4284389054012373</v>
+      </c>
+      <c r="H300" s="334">
+        <v>40.005000000000003</v>
+      </c>
+      <c r="I300" s="335">
+        <v>4.196503986612269E-2</v>
+      </c>
+      <c r="J300" s="336">
+        <v>3.7436375997092319E-2</v>
+      </c>
+      <c r="K300" s="337">
+        <f t="shared" si="21"/>
+        <v>209.57414566045259</v>
+      </c>
+      <c r="L300" s="351"/>
       <c r="M300" s="196"/>
       <c r="N300" s="196"/>
       <c r="O300" s="197"/>
@@ -30059,32 +30156,30 @@
       <c r="Q300" s="196"/>
       <c r="R300" s="198"/>
     </row>
-    <row r="301" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A301" s="6"/>
-      <c r="B301" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C301" s="15"/>
-      <c r="D301" s="15"/>
-      <c r="E301" s="189"/>
-      <c r="F301" s="15"/>
-      <c r="G301" s="15"/>
-      <c r="H301" s="15"/>
-      <c r="I301" s="15"/>
-      <c r="J301" s="15"/>
-      <c r="K301" s="15"/>
-      <c r="L301" s="15"/>
-      <c r="M301" s="15"/>
-      <c r="N301" s="15"/>
-      <c r="O301" s="18"/>
-      <c r="P301" s="7"/>
-      <c r="Q301" s="7"/>
-      <c r="R301" s="90"/>
+    <row r="301" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A301" s="341"/>
+      <c r="B301" s="341"/>
+      <c r="C301" s="341"/>
+      <c r="D301" s="341"/>
+      <c r="E301" s="341"/>
+      <c r="F301" s="341"/>
+      <c r="G301" s="341"/>
+      <c r="H301" s="341"/>
+      <c r="I301" s="341"/>
+      <c r="J301" s="341"/>
+      <c r="K301" s="341"/>
+      <c r="L301" s="260"/>
+      <c r="M301" s="196"/>
+      <c r="N301" s="196"/>
+      <c r="O301" s="197"/>
+      <c r="P301" s="196"/>
+      <c r="Q301" s="196"/>
+      <c r="R301" s="198"/>
     </row>
     <row r="302" spans="1:18" ht="14.4" customHeight="1">
       <c r="A302" s="6"/>
       <c r="B302" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C302" s="15"/>
       <c r="D302" s="15"/>
@@ -30105,8 +30200,8 @@
     </row>
     <row r="303" spans="1:18" ht="14.4" customHeight="1">
       <c r="A303" s="6"/>
-      <c r="B303" s="14" t="s">
-        <v>96</v>
+      <c r="B303" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="C303" s="15"/>
       <c r="D303" s="15"/>
@@ -30127,7 +30222,9 @@
     </row>
     <row r="304" spans="1:18" ht="14.4" customHeight="1">
       <c r="A304" s="6"/>
-      <c r="B304" s="190"/>
+      <c r="B304" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="C304" s="15"/>
       <c r="D304" s="15"/>
       <c r="E304" s="189"/>
@@ -30138,40 +30235,38 @@
       <c r="J304" s="15"/>
       <c r="K304" s="15"/>
       <c r="L304" s="15"/>
-      <c r="M304" s="7"/>
-      <c r="N304" s="7"/>
+      <c r="M304" s="15"/>
+      <c r="N304" s="15"/>
       <c r="O304" s="18"/>
       <c r="P304" s="7"/>
       <c r="Q304" s="7"/>
       <c r="R304" s="90"/>
     </row>
-    <row r="305" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A305" s="49"/>
-      <c r="B305" s="124"/>
-      <c r="C305" s="63" t="s">
+    <row r="305" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A305" s="6"/>
+      <c r="B305" s="190"/>
+      <c r="C305" s="15"/>
+      <c r="D305" s="15"/>
+      <c r="E305" s="189"/>
+      <c r="F305" s="15"/>
+      <c r="G305" s="15"/>
+      <c r="H305" s="15"/>
+      <c r="I305" s="15"/>
+      <c r="J305" s="15"/>
+      <c r="K305" s="15"/>
+      <c r="L305" s="15"/>
+      <c r="M305" s="7"/>
+      <c r="N305" s="7"/>
+      <c r="O305" s="18"/>
+      <c r="P305" s="7"/>
+      <c r="Q305" s="7"/>
+      <c r="R305" s="90"/>
+    </row>
+    <row r="306" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A306" s="49"/>
+      <c r="B306" s="124"/>
+      <c r="C306" s="63" t="s">
         <v>22</v>
-      </c>
-      <c r="D305" s="56"/>
-      <c r="E305" s="189"/>
-      <c r="F305" s="56"/>
-      <c r="G305" s="56"/>
-      <c r="H305" s="56"/>
-      <c r="I305" s="56"/>
-      <c r="J305" s="56"/>
-      <c r="K305" s="56"/>
-      <c r="L305" s="56"/>
-      <c r="M305" s="56"/>
-      <c r="N305" s="56"/>
-      <c r="O305" s="56"/>
-      <c r="P305" s="56"/>
-      <c r="Q305" s="56"/>
-      <c r="R305" s="191"/>
-    </row>
-    <row r="306" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A306" s="49"/>
-      <c r="B306" s="125"/>
-      <c r="C306" s="63" t="s">
-        <v>24</v>
       </c>
       <c r="D306" s="56"/>
       <c r="E306" s="189"/>
@@ -30183,38 +30278,42 @@
       <c r="K306" s="56"/>
       <c r="L306" s="56"/>
       <c r="M306" s="56"/>
-      <c r="N306" s="65"/>
-      <c r="O306" s="7"/>
+      <c r="N306" s="56"/>
+      <c r="O306" s="56"/>
       <c r="P306" s="56"/>
       <c r="Q306" s="56"/>
       <c r="R306" s="191"/>
     </row>
     <row r="307" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A307" s="6"/>
-      <c r="B307" s="83"/>
-      <c r="C307" s="192"/>
-      <c r="D307" s="7"/>
+      <c r="A307" s="49"/>
+      <c r="B307" s="125"/>
+      <c r="C307" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D307" s="56"/>
       <c r="E307" s="189"/>
-      <c r="F307" s="192"/>
-      <c r="G307" s="7"/>
-      <c r="H307" s="192"/>
-      <c r="I307" s="192"/>
-      <c r="J307" s="192"/>
-      <c r="K307" s="192"/>
-      <c r="L307" s="7"/>
-      <c r="M307" s="7"/>
-      <c r="N307" s="7"/>
+      <c r="F307" s="56"/>
+      <c r="G307" s="56"/>
+      <c r="H307" s="56"/>
+      <c r="I307" s="56"/>
+      <c r="J307" s="56"/>
+      <c r="K307" s="56"/>
+      <c r="L307" s="56"/>
+      <c r="M307" s="56"/>
+      <c r="N307" s="65"/>
       <c r="O307" s="7"/>
-      <c r="P307" s="7"/>
-      <c r="Q307" s="7"/>
-      <c r="R307" s="90"/>
+      <c r="P307" s="56"/>
+      <c r="Q307" s="56"/>
+      <c r="R307" s="191"/>
     </row>
     <row r="308" spans="1:18" ht="14.4" customHeight="1">
       <c r="A308" s="6"/>
-      <c r="B308" s="7"/>
-      <c r="C308" s="192"/>
-      <c r="D308" s="7"/>
-      <c r="E308" s="189"/>
+      <c r="B308" s="62"/>
+      <c r="C308" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D308" s="56"/>
+      <c r="E308" s="56"/>
       <c r="F308" s="192"/>
       <c r="G308" s="7"/>
       <c r="H308" s="192"/>
@@ -30230,27 +30329,44 @@
       <c r="R308" s="90"/>
     </row>
     <row r="309" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A309" s="85"/>
-      <c r="B309" s="86"/>
-      <c r="C309" s="193"/>
-      <c r="D309" s="86"/>
-      <c r="E309" s="86"/>
-      <c r="F309" s="193"/>
-      <c r="G309" s="86"/>
-      <c r="H309" s="193"/>
-      <c r="I309" s="193"/>
-      <c r="J309" s="193"/>
-      <c r="K309" s="193"/>
-      <c r="L309" s="86"/>
-      <c r="M309" s="86"/>
-      <c r="N309" s="86"/>
-      <c r="O309" s="86"/>
-      <c r="P309" s="86"/>
-      <c r="Q309" s="86"/>
-      <c r="R309" s="129"/>
-    </row>
-    <row r="312" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C312" s="284"/>
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
+      <c r="C309" s="192"/>
+      <c r="D309" s="7"/>
+      <c r="E309" s="189"/>
+      <c r="F309" s="192"/>
+      <c r="G309" s="7"/>
+      <c r="H309" s="192"/>
+      <c r="I309" s="192"/>
+      <c r="J309" s="192"/>
+      <c r="K309" s="192"/>
+      <c r="L309" s="7"/>
+      <c r="M309" s="7"/>
+      <c r="N309" s="7"/>
+      <c r="O309" s="7"/>
+      <c r="P309" s="7"/>
+      <c r="Q309" s="7"/>
+      <c r="R309" s="90"/>
+    </row>
+    <row r="310" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A310" s="85"/>
+      <c r="B310" s="86"/>
+      <c r="C310" s="193"/>
+      <c r="D310" s="86"/>
+      <c r="E310" s="86"/>
+      <c r="F310" s="193"/>
+      <c r="G310" s="86"/>
+      <c r="H310" s="193"/>
+      <c r="I310" s="193"/>
+      <c r="J310" s="193"/>
+      <c r="K310" s="193"/>
+      <c r="L310" s="86"/>
+      <c r="M310" s="86"/>
+      <c r="N310" s="86"/>
+      <c r="O310" s="86"/>
+      <c r="P310" s="86"/>
+      <c r="Q310" s="86"/>
+      <c r="R310" s="129"/>
     </row>
     <row r="313" spans="1:18" ht="14.4" customHeight="1">
       <c r="C313" s="284"/>
@@ -30278,6 +30394,9 @@
     </row>
     <row r="321" spans="3:3" ht="14.4" customHeight="1">
       <c r="C321" s="284"/>
+    </row>
+    <row r="322" spans="3:3" ht="14.4" customHeight="1">
+      <c r="C322" s="284"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30331,15 +30450,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -30580,6 +30690,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -30592,14 +30711,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BA7FD74-EE25-42EE-BD44-8280994753BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30618,6 +30729,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
   <ds:schemaRefs>

--- a/data_raw/precio_leche_productor.xlsx
+++ b/data_raw/precio_leche_productor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/1- Producción y precios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1311" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827EC136-D3C3-4E04-A771-6B3C29952959}"/>
+  <xr:revisionPtr revIDLastSave="1398" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6611D53-024D-4D00-88F1-DD35723A4858}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2260,7 +2260,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="379">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2925,6 +2925,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3170,16 +3174,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>279432</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114689</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>469932</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>8009</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3202,8 +3206,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6964680" y="38100"/>
-          <a:ext cx="2092992" cy="1539629"/>
+          <a:off x="6629400" y="121920"/>
+          <a:ext cx="2199672" cy="1539629"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4419,22 +4423,22 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.44140625" style="1" customWidth="1"/>
     <col min="8" max="9" width="7.44140625" style="1" customWidth="1"/>
     <col min="10" max="11" width="6.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.109375" style="1" customWidth="1"/>
     <col min="13" max="14" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="6" style="1" customWidth="1"/>
     <col min="17" max="17" width="9.44140625" style="1" customWidth="1"/>
     <col min="18" max="18" width="5.33203125" style="1" customWidth="1"/>
     <col min="19" max="19" width="3.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7" style="1" customWidth="1"/>
     <col min="21" max="22" width="7.88671875" style="1" customWidth="1"/>
     <col min="23" max="23" width="6.44140625" style="1" customWidth="1"/>
     <col min="24" max="24" width="7.88671875" style="1" customWidth="1"/>
@@ -4815,17 +4819,17 @@
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="359" t="s">
+      <c r="E10" s="361" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="360"/>
-      <c r="G10" s="360"/>
-      <c r="H10" s="360"/>
-      <c r="I10" s="360"/>
-      <c r="J10" s="360"/>
-      <c r="K10" s="360"/>
-      <c r="L10" s="360"/>
-      <c r="M10" s="361"/>
+      <c r="F10" s="362"/>
+      <c r="G10" s="362"/>
+      <c r="H10" s="362"/>
+      <c r="I10" s="362"/>
+      <c r="J10" s="362"/>
+      <c r="K10" s="362"/>
+      <c r="L10" s="362"/>
+      <c r="M10" s="363"/>
       <c r="N10" s="17"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -4835,17 +4839,17 @@
       <c r="T10" s="19"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="356" t="s">
+      <c r="W10" s="358" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="357"/>
-      <c r="Y10" s="357"/>
-      <c r="Z10" s="357"/>
-      <c r="AA10" s="357"/>
-      <c r="AB10" s="357"/>
-      <c r="AC10" s="357"/>
-      <c r="AD10" s="357"/>
-      <c r="AE10" s="358"/>
+      <c r="X10" s="359"/>
+      <c r="Y10" s="359"/>
+      <c r="Z10" s="359"/>
+      <c r="AA10" s="359"/>
+      <c r="AB10" s="359"/>
+      <c r="AC10" s="359"/>
+      <c r="AD10" s="359"/>
+      <c r="AE10" s="360"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
@@ -7730,22 +7734,26 @@
         <v>2026</v>
       </c>
       <c r="C37" s="354">
-        <v>16.087724443768948</v>
+        <v>16.03</v>
       </c>
       <c r="D37" s="355">
-        <v>16.511849716258542</v>
+        <v>16.38</v>
       </c>
       <c r="E37" s="355">
-        <v>16.88282948579424</v>
-      </c>
-      <c r="F37" s="339">
-        <v>16.688703974646522</v>
-      </c>
-      <c r="G37" s="339">
-        <v>17.1396984105765</v>
-      </c>
-      <c r="H37" s="303"/>
-      <c r="I37" s="303"/>
+        <v>16.79</v>
+      </c>
+      <c r="F37" s="353">
+        <v>16.64</v>
+      </c>
+      <c r="G37" s="353">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="H37" s="339">
+        <v>16.904922634102324</v>
+      </c>
+      <c r="I37" s="339">
+        <v>16.66087764035127</v>
+      </c>
       <c r="J37" s="303"/>
       <c r="K37" s="303"/>
       <c r="L37" s="303"/>
@@ -7768,14 +7776,18 @@
       <c r="W37" s="353">
         <v>16.79</v>
       </c>
-      <c r="X37" s="339">
-        <v>16.688703974646522</v>
-      </c>
-      <c r="Y37" s="339">
-        <v>17.1396984105765</v>
-      </c>
-      <c r="Z37" s="303"/>
-      <c r="AA37" s="303"/>
+      <c r="X37" s="353">
+        <v>16.64</v>
+      </c>
+      <c r="Y37" s="353">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="Z37" s="339">
+        <v>16.904922634102324</v>
+      </c>
+      <c r="AA37" s="339">
+        <v>16.66087764035127</v>
+      </c>
       <c r="AB37" s="303"/>
       <c r="AC37" s="303"/>
       <c r="AD37" s="303"/>
@@ -7885,8 +7897,8 @@
       <c r="N40" s="56"/>
       <c r="O40" s="56"/>
       <c r="P40" s="56"/>
-      <c r="Q40" s="261"/>
-      <c r="R40" s="261"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
       <c r="S40" s="56"/>
       <c r="T40" s="56"/>
       <c r="U40" s="56"/>
@@ -8073,23 +8085,23 @@
     </row>
     <row r="45" spans="1:37" ht="36" customHeight="1">
       <c r="A45" s="68"/>
-      <c r="B45" s="362"/>
-      <c r="C45" s="363"/>
-      <c r="D45" s="363"/>
-      <c r="E45" s="364"/>
-      <c r="F45" s="364"/>
-      <c r="G45" s="364"/>
-      <c r="H45" s="364"/>
-      <c r="I45" s="364"/>
-      <c r="J45" s="364"/>
-      <c r="K45" s="364"/>
-      <c r="L45" s="364"/>
-      <c r="M45" s="364"/>
-      <c r="N45" s="363"/>
-      <c r="O45" s="363"/>
-      <c r="P45" s="363"/>
-      <c r="Q45" s="363"/>
-      <c r="R45" s="363"/>
+      <c r="B45" s="364"/>
+      <c r="C45" s="365"/>
+      <c r="D45" s="365"/>
+      <c r="E45" s="366"/>
+      <c r="F45" s="366"/>
+      <c r="G45" s="366"/>
+      <c r="H45" s="366"/>
+      <c r="I45" s="366"/>
+      <c r="J45" s="366"/>
+      <c r="K45" s="366"/>
+      <c r="L45" s="366"/>
+      <c r="M45" s="366"/>
+      <c r="N45" s="365"/>
+      <c r="O45" s="365"/>
+      <c r="P45" s="365"/>
+      <c r="Q45" s="365"/>
+      <c r="R45" s="365"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
@@ -8115,17 +8127,17 @@
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="69"/>
-      <c r="E46" s="359" t="s">
+      <c r="E46" s="361" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="360"/>
-      <c r="G46" s="360"/>
-      <c r="H46" s="360"/>
-      <c r="I46" s="360"/>
-      <c r="J46" s="360"/>
-      <c r="K46" s="360"/>
-      <c r="L46" s="360"/>
-      <c r="M46" s="361"/>
+      <c r="F46" s="362"/>
+      <c r="G46" s="362"/>
+      <c r="H46" s="362"/>
+      <c r="I46" s="362"/>
+      <c r="J46" s="362"/>
+      <c r="K46" s="362"/>
+      <c r="L46" s="362"/>
+      <c r="M46" s="363"/>
       <c r="N46" s="70"/>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -8135,17 +8147,17 @@
       <c r="T46" s="71"/>
       <c r="U46" s="7"/>
       <c r="V46" s="69"/>
-      <c r="W46" s="356" t="s">
+      <c r="W46" s="358" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="357"/>
-      <c r="Y46" s="357"/>
-      <c r="Z46" s="357"/>
-      <c r="AA46" s="357"/>
-      <c r="AB46" s="357"/>
-      <c r="AC46" s="357"/>
-      <c r="AD46" s="357"/>
-      <c r="AE46" s="358"/>
+      <c r="X46" s="359"/>
+      <c r="Y46" s="359"/>
+      <c r="Z46" s="359"/>
+      <c r="AA46" s="359"/>
+      <c r="AB46" s="359"/>
+      <c r="AC46" s="359"/>
+      <c r="AD46" s="359"/>
+      <c r="AE46" s="360"/>
       <c r="AF46" s="70"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="7"/>
@@ -11011,14 +11023,18 @@
       <c r="E73" s="353">
         <v>0.41705996323712052</v>
       </c>
-      <c r="F73" s="339">
-        <v>0.41712374652319534</v>
-      </c>
-      <c r="G73" s="339">
-        <v>0.4284389054012373</v>
-      </c>
-      <c r="H73" s="303"/>
-      <c r="I73" s="303"/>
+      <c r="F73" s="353">
+        <v>0.4159064210552626</v>
+      </c>
+      <c r="G73" s="353">
+        <v>0.42644669416322956</v>
+      </c>
+      <c r="H73" s="339">
+        <v>0.41983118844936979</v>
+      </c>
+      <c r="I73" s="339">
+        <v>0.41441876577248637</v>
+      </c>
       <c r="J73" s="303"/>
       <c r="K73" s="303"/>
       <c r="L73" s="303"/>
@@ -11041,14 +11057,18 @@
       <c r="W73" s="353">
         <v>0.41705996323712052</v>
       </c>
-      <c r="X73" s="339">
-        <v>0.41712374652319534</v>
-      </c>
-      <c r="Y73" s="339">
-        <v>0.4284389054012373</v>
-      </c>
-      <c r="Z73" s="303"/>
-      <c r="AA73" s="303"/>
+      <c r="X73" s="353">
+        <v>0.4159064210552626</v>
+      </c>
+      <c r="Y73" s="353">
+        <v>0.42644669416322956</v>
+      </c>
+      <c r="Z73" s="339">
+        <v>0.41983118844936979</v>
+      </c>
+      <c r="AA73" s="339">
+        <v>0.41441876577248637</v>
+      </c>
       <c r="AB73" s="303"/>
       <c r="AC73" s="303"/>
       <c r="AD73" s="303"/>
@@ -11347,23 +11367,23 @@
     </row>
     <row r="81" spans="1:37" ht="19.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="362"/>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="364"/>
-      <c r="G81" s="364"/>
-      <c r="H81" s="364"/>
-      <c r="I81" s="364"/>
-      <c r="J81" s="364"/>
-      <c r="K81" s="363"/>
-      <c r="L81" s="363"/>
-      <c r="M81" s="363"/>
-      <c r="N81" s="363"/>
-      <c r="O81" s="363"/>
-      <c r="P81" s="363"/>
-      <c r="Q81" s="363"/>
-      <c r="R81" s="363"/>
+      <c r="B81" s="364"/>
+      <c r="C81" s="365"/>
+      <c r="D81" s="365"/>
+      <c r="E81" s="365"/>
+      <c r="F81" s="366"/>
+      <c r="G81" s="366"/>
+      <c r="H81" s="366"/>
+      <c r="I81" s="366"/>
+      <c r="J81" s="366"/>
+      <c r="K81" s="365"/>
+      <c r="L81" s="365"/>
+      <c r="M81" s="365"/>
+      <c r="N81" s="365"/>
+      <c r="O81" s="365"/>
+      <c r="P81" s="365"/>
+      <c r="Q81" s="365"/>
+      <c r="R81" s="365"/>
       <c r="S81" s="7"/>
       <c r="T81" s="57"/>
       <c r="U81" s="56"/>
@@ -11390,13 +11410,13 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="69"/>
-      <c r="F82" s="356" t="s">
+      <c r="F82" s="358" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="357"/>
-      <c r="H82" s="357"/>
-      <c r="I82" s="357"/>
-      <c r="J82" s="358"/>
+      <c r="G82" s="359"/>
+      <c r="H82" s="359"/>
+      <c r="I82" s="359"/>
+      <c r="J82" s="360"/>
       <c r="K82" s="70"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -13254,8 +13274,12 @@
       <c r="G109" s="46">
         <v>40.005000000000003</v>
       </c>
-      <c r="H109" s="46"/>
-      <c r="I109" s="46"/>
+      <c r="H109" s="46">
+        <v>40.265999999999998</v>
+      </c>
+      <c r="I109" s="46">
+        <v>40.203000000000003</v>
+      </c>
       <c r="J109" s="46"/>
       <c r="K109" s="46"/>
       <c r="L109" s="46"/>
@@ -13902,13 +13926,13 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="69"/>
-      <c r="F10" s="365" t="s">
+      <c r="F10" s="367" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="366"/>
-      <c r="H10" s="366"/>
-      <c r="I10" s="366"/>
-      <c r="J10" s="367"/>
+      <c r="G10" s="368"/>
+      <c r="H10" s="368"/>
+      <c r="I10" s="368"/>
+      <c r="J10" s="369"/>
       <c r="K10" s="70"/>
       <c r="L10" s="12" t="s">
         <v>2</v>
@@ -13945,11 +13969,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="368" t="s">
+      <c r="G12" s="370" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="369"/>
-      <c r="I12" s="370"/>
+      <c r="H12" s="371"/>
+      <c r="I12" s="372"/>
       <c r="J12" s="70"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -14744,8 +14768,12 @@
       <c r="G29" s="104">
         <v>4.196503986612269E-2</v>
       </c>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
+      <c r="H29" s="104">
+        <v>4.1255608911305482E-2</v>
+      </c>
+      <c r="I29" s="104">
+        <v>4.0831668392197998E-2</v>
+      </c>
       <c r="J29" s="104"/>
       <c r="K29" s="104"/>
       <c r="L29" s="104"/>
@@ -14824,11 +14852,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="371" t="s">
+      <c r="G33" s="373" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="372"/>
-      <c r="I33" s="373"/>
+      <c r="H33" s="374"/>
+      <c r="I33" s="375"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -15621,8 +15649,12 @@
       <c r="G50" s="104">
         <v>3.7436375997092319E-2</v>
       </c>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
+      <c r="H50" s="104">
+        <v>3.6966638448907747E-2</v>
+      </c>
+      <c r="I50" s="104">
+        <v>3.6481081617249909E-2</v>
+      </c>
       <c r="J50" s="104"/>
       <c r="K50" s="104"/>
       <c r="L50" s="104"/>
@@ -15699,13 +15731,13 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="69"/>
-      <c r="F54" s="374" t="s">
+      <c r="F54" s="376" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="375"/>
-      <c r="H54" s="375"/>
-      <c r="I54" s="375"/>
-      <c r="J54" s="375"/>
+      <c r="G54" s="377"/>
+      <c r="H54" s="377"/>
+      <c r="I54" s="377"/>
+      <c r="J54" s="377"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -16492,13 +16524,17 @@
         <v>206.82416724265303</v>
       </c>
       <c r="F71" s="202">
-        <v>207.10704035784963</v>
-      </c>
-      <c r="G71" s="202">
-        <v>209.57414566045259</v>
-      </c>
-      <c r="H71" s="202"/>
-      <c r="I71" s="202"/>
+        <v>206.50262337867446</v>
+      </c>
+      <c r="G71" s="357">
+        <v>208.59964039746853</v>
+      </c>
+      <c r="H71" s="357">
+        <v>209.81941583858563</v>
+      </c>
+      <c r="I71" s="202">
+        <v>209.22304998318674</v>
+      </c>
       <c r="J71" s="202"/>
       <c r="K71" s="202"/>
       <c r="L71" s="202"/>
@@ -16715,7 +16751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R322"/>
+  <dimension ref="A1:R324"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
@@ -16819,17 +16855,17 @@
     <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="131"/>
-      <c r="C5" s="376" t="s">
+      <c r="C5" s="378" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="377"/>
-      <c r="E5" s="377"/>
-      <c r="F5" s="377"/>
-      <c r="G5" s="377"/>
-      <c r="H5" s="377"/>
-      <c r="I5" s="377"/>
-      <c r="J5" s="377"/>
-      <c r="K5" s="378"/>
+      <c r="D5" s="379"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="379"/>
+      <c r="J5" s="379"/>
+      <c r="K5" s="380"/>
       <c r="L5" s="70"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -28497,11 +28533,11 @@
         <v>17.61</v>
       </c>
       <c r="F264" s="203">
-        <f t="shared" ref="F264:F300" si="18">C264/H264</f>
+        <f t="shared" ref="F264:F301" si="18">C264/H264</f>
         <v>0.45315354725817658</v>
       </c>
       <c r="G264" s="204">
-        <f t="shared" ref="G264:G300" si="19">E264/H264</f>
+        <f t="shared" ref="G264:G301" si="19">E264/H264</f>
         <v>0.45315354725817658</v>
       </c>
       <c r="H264" s="205">
@@ -28783,7 +28819,7 @@
         <v>3.4547912831612973E-2</v>
       </c>
       <c r="K270" s="238">
-        <f t="shared" ref="K270:K300" si="21">C270/1.03/(I270+J270)</f>
+        <f t="shared" ref="K270:K301" si="21">C270/1.03/(I270+J270)</f>
         <v>192.128050061945</v>
       </c>
       <c r="L270" s="241" t="s">
@@ -29988,7 +30024,7 @@
         <v>46054</v>
       </c>
       <c r="C297" s="225">
-        <f t="shared" ref="C297:C298" si="23">E297</f>
+        <f t="shared" ref="C297:C300" si="23">E297</f>
         <v>16.38</v>
       </c>
       <c r="D297" s="225">
@@ -30072,40 +30108,41 @@
     </row>
     <row r="299" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A299" s="196"/>
-      <c r="B299" s="348">
+      <c r="B299" s="236">
         <v>46113</v>
       </c>
-      <c r="C299" s="277">
-        <v>16.688703974646522</v>
-      </c>
-      <c r="D299" s="277">
+      <c r="C299" s="225">
+        <f t="shared" si="23"/>
+        <v>16.64</v>
+      </c>
+      <c r="D299" s="225">
         <v>7.2386235954015445E-3</v>
       </c>
-      <c r="E299" s="276">
-        <v>16.688703974646522</v>
-      </c>
-      <c r="F299" s="278">
+      <c r="E299" s="249">
+        <v>16.64</v>
+      </c>
+      <c r="F299" s="203">
         <f t="shared" si="18"/>
-        <v>0.41712374652319534</v>
-      </c>
-      <c r="G299" s="279">
+        <v>0.4159064210552626</v>
+      </c>
+      <c r="G299" s="204">
         <f t="shared" si="19"/>
-        <v>0.41712374652319534</v>
-      </c>
-      <c r="H299" s="280">
+        <v>0.4159064210552626</v>
+      </c>
+      <c r="H299" s="205">
         <v>40.009</v>
       </c>
-      <c r="I299" s="281">
+      <c r="I299" s="206">
         <v>4.1966373257041917E-2</v>
       </c>
-      <c r="J299" s="282">
+      <c r="J299" s="207">
         <v>3.6266723938049715E-2</v>
       </c>
-      <c r="K299" s="283">
+      <c r="K299" s="238">
         <f t="shared" si="21"/>
-        <v>207.10704035784963</v>
-      </c>
-      <c r="L299" s="349"/>
+        <v>206.50262337867446</v>
+      </c>
+      <c r="L299" s="356"/>
       <c r="M299" s="196"/>
       <c r="N299" s="196"/>
       <c r="O299" s="197"/>
@@ -30115,40 +30152,41 @@
     </row>
     <row r="300" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A300" s="341"/>
-      <c r="B300" s="350">
+      <c r="B300" s="236">
         <v>46143</v>
       </c>
-      <c r="C300" s="330">
-        <v>17.1396984105765</v>
-      </c>
-      <c r="D300" s="330">
+      <c r="C300" s="225">
+        <f t="shared" si="23"/>
+        <v>17.059999999999999</v>
+      </c>
+      <c r="D300" s="225">
         <v>7.9065318674885494E-3</v>
       </c>
-      <c r="E300" s="331">
-        <v>17.1396984105765</v>
-      </c>
-      <c r="F300" s="332">
+      <c r="E300" s="249">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="F300" s="203">
         <f t="shared" si="18"/>
-        <v>0.4284389054012373</v>
-      </c>
-      <c r="G300" s="333">
+        <v>0.42644669416322956</v>
+      </c>
+      <c r="G300" s="204">
         <f t="shared" si="19"/>
-        <v>0.4284389054012373</v>
-      </c>
-      <c r="H300" s="334">
+        <v>0.42644669416322956</v>
+      </c>
+      <c r="H300" s="205">
         <v>40.005000000000003</v>
       </c>
-      <c r="I300" s="335">
+      <c r="I300" s="206">
         <v>4.196503986612269E-2</v>
       </c>
-      <c r="J300" s="336">
+      <c r="J300" s="207">
         <v>3.7436375997092319E-2</v>
       </c>
-      <c r="K300" s="337">
+      <c r="K300" s="238">
         <f t="shared" si="21"/>
-        <v>209.57414566045259</v>
-      </c>
-      <c r="L300" s="351"/>
+        <v>208.59964039746853</v>
+      </c>
+      <c r="L300" s="356"/>
       <c r="M300" s="196"/>
       <c r="N300" s="196"/>
       <c r="O300" s="197"/>
@@ -30158,17 +30196,40 @@
     </row>
     <row r="301" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A301" s="341"/>
-      <c r="B301" s="341"/>
-      <c r="C301" s="341"/>
-      <c r="D301" s="341"/>
-      <c r="E301" s="341"/>
-      <c r="F301" s="341"/>
-      <c r="G301" s="341"/>
-      <c r="H301" s="341"/>
-      <c r="I301" s="341"/>
-      <c r="J301" s="341"/>
-      <c r="K301" s="341"/>
-      <c r="L301" s="260"/>
+      <c r="B301" s="348">
+        <v>46174</v>
+      </c>
+      <c r="C301" s="277">
+        <v>16.904922634102324</v>
+      </c>
+      <c r="D301" s="277">
+        <v>7.3942392978635467E-3</v>
+      </c>
+      <c r="E301" s="276">
+        <v>16.904922634102324</v>
+      </c>
+      <c r="F301" s="278">
+        <f t="shared" si="18"/>
+        <v>0.41983118844936979</v>
+      </c>
+      <c r="G301" s="279">
+        <f t="shared" si="19"/>
+        <v>0.41983118844936979</v>
+      </c>
+      <c r="H301" s="280">
+        <v>40.265999999999998</v>
+      </c>
+      <c r="I301" s="281">
+        <v>4.1255608911305482E-2</v>
+      </c>
+      <c r="J301" s="282">
+        <v>3.6966638448907747E-2</v>
+      </c>
+      <c r="K301" s="283">
+        <f t="shared" si="21"/>
+        <v>209.81941583858563</v>
+      </c>
+      <c r="L301" s="349"/>
       <c r="M301" s="196"/>
       <c r="N301" s="196"/>
       <c r="O301" s="197"/>
@@ -30176,54 +30237,70 @@
       <c r="Q301" s="196"/>
       <c r="R301" s="198"/>
     </row>
-    <row r="302" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A302" s="6"/>
-      <c r="B302" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C302" s="15"/>
-      <c r="D302" s="15"/>
-      <c r="E302" s="189"/>
-      <c r="F302" s="15"/>
-      <c r="G302" s="15"/>
-      <c r="H302" s="15"/>
-      <c r="I302" s="15"/>
-      <c r="J302" s="15"/>
-      <c r="K302" s="15"/>
-      <c r="L302" s="15"/>
-      <c r="M302" s="15"/>
-      <c r="N302" s="15"/>
-      <c r="O302" s="18"/>
-      <c r="P302" s="7"/>
-      <c r="Q302" s="7"/>
-      <c r="R302" s="90"/>
-    </row>
-    <row r="303" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A303" s="6"/>
-      <c r="B303" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C303" s="15"/>
-      <c r="D303" s="15"/>
-      <c r="E303" s="189"/>
-      <c r="F303" s="15"/>
-      <c r="G303" s="15"/>
-      <c r="H303" s="15"/>
-      <c r="I303" s="15"/>
-      <c r="J303" s="15"/>
-      <c r="K303" s="15"/>
-      <c r="L303" s="15"/>
-      <c r="M303" s="15"/>
-      <c r="N303" s="15"/>
-      <c r="O303" s="18"/>
-      <c r="P303" s="7"/>
-      <c r="Q303" s="7"/>
-      <c r="R303" s="90"/>
+    <row r="302" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A302" s="341"/>
+      <c r="B302" s="350">
+        <v>46204</v>
+      </c>
+      <c r="C302" s="330">
+        <v>16.66087764035127</v>
+      </c>
+      <c r="D302" s="330">
+        <v>7.7522292811096826E-3</v>
+      </c>
+      <c r="E302" s="331">
+        <v>16.66087764035127</v>
+      </c>
+      <c r="F302" s="332">
+        <v>0.41441876577248637</v>
+      </c>
+      <c r="G302" s="333">
+        <v>0.41441876577248637</v>
+      </c>
+      <c r="H302" s="334">
+        <v>40.203000000000003</v>
+      </c>
+      <c r="I302" s="335">
+        <v>4.0831668392197998E-2</v>
+      </c>
+      <c r="J302" s="336">
+        <v>3.6481081617249909E-2</v>
+      </c>
+      <c r="K302" s="337">
+        <v>209.22304998318674</v>
+      </c>
+      <c r="L302" s="351"/>
+      <c r="M302" s="196"/>
+      <c r="N302" s="196"/>
+      <c r="O302" s="197"/>
+      <c r="P302" s="196"/>
+      <c r="Q302" s="196"/>
+      <c r="R302" s="198"/>
+    </row>
+    <row r="303" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A303" s="341"/>
+      <c r="B303" s="341"/>
+      <c r="C303" s="341"/>
+      <c r="D303" s="341"/>
+      <c r="E303" s="341"/>
+      <c r="F303" s="341"/>
+      <c r="G303" s="341"/>
+      <c r="H303" s="341"/>
+      <c r="I303" s="341"/>
+      <c r="J303" s="341"/>
+      <c r="K303" s="341"/>
+      <c r="L303" s="260"/>
+      <c r="M303" s="196"/>
+      <c r="N303" s="196"/>
+      <c r="O303" s="197"/>
+      <c r="P303" s="196"/>
+      <c r="Q303" s="196"/>
+      <c r="R303" s="198"/>
     </row>
     <row r="304" spans="1:18" ht="14.4" customHeight="1">
       <c r="A304" s="6"/>
-      <c r="B304" s="14" t="s">
-        <v>96</v>
+      <c r="B304" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="C304" s="15"/>
       <c r="D304" s="15"/>
@@ -30244,7 +30321,9 @@
     </row>
     <row r="305" spans="1:18" ht="14.4" customHeight="1">
       <c r="A305" s="6"/>
-      <c r="B305" s="190"/>
+      <c r="B305" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="C305" s="15"/>
       <c r="D305" s="15"/>
       <c r="E305" s="189"/>
@@ -30255,124 +30334,160 @@
       <c r="J305" s="15"/>
       <c r="K305" s="15"/>
       <c r="L305" s="15"/>
-      <c r="M305" s="7"/>
-      <c r="N305" s="7"/>
+      <c r="M305" s="15"/>
+      <c r="N305" s="15"/>
       <c r="O305" s="18"/>
       <c r="P305" s="7"/>
       <c r="Q305" s="7"/>
       <c r="R305" s="90"/>
     </row>
-    <row r="306" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A306" s="49"/>
-      <c r="B306" s="124"/>
-      <c r="C306" s="63" t="s">
+    <row r="306" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A306" s="6"/>
+      <c r="B306" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C306" s="15"/>
+      <c r="D306" s="15"/>
+      <c r="E306" s="189"/>
+      <c r="F306" s="15"/>
+      <c r="G306" s="15"/>
+      <c r="H306" s="15"/>
+      <c r="I306" s="15"/>
+      <c r="J306" s="15"/>
+      <c r="K306" s="15"/>
+      <c r="L306" s="15"/>
+      <c r="M306" s="15"/>
+      <c r="N306" s="15"/>
+      <c r="O306" s="18"/>
+      <c r="P306" s="7"/>
+      <c r="Q306" s="7"/>
+      <c r="R306" s="90"/>
+    </row>
+    <row r="307" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A307" s="6"/>
+      <c r="B307" s="190"/>
+      <c r="C307" s="15"/>
+      <c r="D307" s="15"/>
+      <c r="E307" s="189"/>
+      <c r="F307" s="15"/>
+      <c r="G307" s="15"/>
+      <c r="H307" s="15"/>
+      <c r="I307" s="15"/>
+      <c r="J307" s="15"/>
+      <c r="K307" s="15"/>
+      <c r="L307" s="15"/>
+      <c r="M307" s="7"/>
+      <c r="N307" s="7"/>
+      <c r="O307" s="18"/>
+      <c r="P307" s="7"/>
+      <c r="Q307" s="7"/>
+      <c r="R307" s="90"/>
+    </row>
+    <row r="308" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A308" s="49"/>
+      <c r="B308" s="124"/>
+      <c r="C308" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D306" s="56"/>
-      <c r="E306" s="189"/>
-      <c r="F306" s="56"/>
-      <c r="G306" s="56"/>
-      <c r="H306" s="56"/>
-      <c r="I306" s="56"/>
-      <c r="J306" s="56"/>
-      <c r="K306" s="56"/>
-      <c r="L306" s="56"/>
-      <c r="M306" s="56"/>
-      <c r="N306" s="56"/>
-      <c r="O306" s="56"/>
-      <c r="P306" s="56"/>
-      <c r="Q306" s="56"/>
-      <c r="R306" s="191"/>
-    </row>
-    <row r="307" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A307" s="49"/>
-      <c r="B307" s="125"/>
-      <c r="C307" s="63" t="s">
+      <c r="D308" s="56"/>
+      <c r="E308" s="189"/>
+      <c r="F308" s="56"/>
+      <c r="G308" s="56"/>
+      <c r="H308" s="56"/>
+      <c r="I308" s="56"/>
+      <c r="J308" s="56"/>
+      <c r="K308" s="56"/>
+      <c r="L308" s="56"/>
+      <c r="M308" s="56"/>
+      <c r="N308" s="56"/>
+      <c r="O308" s="56"/>
+      <c r="P308" s="56"/>
+      <c r="Q308" s="56"/>
+      <c r="R308" s="191"/>
+    </row>
+    <row r="309" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A309" s="49"/>
+      <c r="B309" s="125"/>
+      <c r="C309" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D307" s="56"/>
-      <c r="E307" s="189"/>
-      <c r="F307" s="56"/>
-      <c r="G307" s="56"/>
-      <c r="H307" s="56"/>
-      <c r="I307" s="56"/>
-      <c r="J307" s="56"/>
-      <c r="K307" s="56"/>
-      <c r="L307" s="56"/>
-      <c r="M307" s="56"/>
-      <c r="N307" s="65"/>
-      <c r="O307" s="7"/>
-      <c r="P307" s="56"/>
-      <c r="Q307" s="56"/>
-      <c r="R307" s="191"/>
-    </row>
-    <row r="308" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A308" s="6"/>
-      <c r="B308" s="62"/>
-      <c r="C308" s="63" t="s">
+      <c r="D309" s="56"/>
+      <c r="E309" s="189"/>
+      <c r="F309" s="56"/>
+      <c r="G309" s="56"/>
+      <c r="H309" s="56"/>
+      <c r="I309" s="56"/>
+      <c r="J309" s="56"/>
+      <c r="K309" s="56"/>
+      <c r="L309" s="56"/>
+      <c r="M309" s="56"/>
+      <c r="N309" s="65"/>
+      <c r="O309" s="7"/>
+      <c r="P309" s="56"/>
+      <c r="Q309" s="56"/>
+      <c r="R309" s="191"/>
+    </row>
+    <row r="310" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A310" s="6"/>
+      <c r="B310" s="62"/>
+      <c r="C310" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D308" s="56"/>
-      <c r="E308" s="56"/>
-      <c r="F308" s="192"/>
-      <c r="G308" s="7"/>
-      <c r="H308" s="192"/>
-      <c r="I308" s="192"/>
-      <c r="J308" s="192"/>
-      <c r="K308" s="192"/>
-      <c r="L308" s="7"/>
-      <c r="M308" s="7"/>
-      <c r="N308" s="7"/>
-      <c r="O308" s="7"/>
-      <c r="P308" s="7"/>
-      <c r="Q308" s="7"/>
-      <c r="R308" s="90"/>
-    </row>
-    <row r="309" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A309" s="6"/>
-      <c r="B309" s="7"/>
-      <c r="C309" s="192"/>
-      <c r="D309" s="7"/>
-      <c r="E309" s="189"/>
-      <c r="F309" s="192"/>
-      <c r="G309" s="7"/>
-      <c r="H309" s="192"/>
-      <c r="I309" s="192"/>
-      <c r="J309" s="192"/>
-      <c r="K309" s="192"/>
-      <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
-      <c r="N309" s="7"/>
-      <c r="O309" s="7"/>
-      <c r="P309" s="7"/>
-      <c r="Q309" s="7"/>
-      <c r="R309" s="90"/>
-    </row>
-    <row r="310" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A310" s="85"/>
-      <c r="B310" s="86"/>
-      <c r="C310" s="193"/>
-      <c r="D310" s="86"/>
-      <c r="E310" s="86"/>
-      <c r="F310" s="193"/>
-      <c r="G310" s="86"/>
-      <c r="H310" s="193"/>
-      <c r="I310" s="193"/>
-      <c r="J310" s="193"/>
-      <c r="K310" s="193"/>
-      <c r="L310" s="86"/>
-      <c r="M310" s="86"/>
-      <c r="N310" s="86"/>
-      <c r="O310" s="86"/>
-      <c r="P310" s="86"/>
-      <c r="Q310" s="86"/>
-      <c r="R310" s="129"/>
-    </row>
-    <row r="313" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C313" s="284"/>
-    </row>
-    <row r="314" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C314" s="284"/>
+      <c r="D310" s="56"/>
+      <c r="E310" s="56"/>
+      <c r="F310" s="192"/>
+      <c r="G310" s="7"/>
+      <c r="H310" s="192"/>
+      <c r="I310" s="192"/>
+      <c r="J310" s="192"/>
+      <c r="K310" s="192"/>
+      <c r="L310" s="7"/>
+      <c r="M310" s="7"/>
+      <c r="N310" s="7"/>
+      <c r="O310" s="7"/>
+      <c r="P310" s="7"/>
+      <c r="Q310" s="7"/>
+      <c r="R310" s="90"/>
+    </row>
+    <row r="311" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A311" s="6"/>
+      <c r="B311" s="7"/>
+      <c r="C311" s="192"/>
+      <c r="D311" s="7"/>
+      <c r="E311" s="189"/>
+      <c r="F311" s="192"/>
+      <c r="G311" s="7"/>
+      <c r="H311" s="192"/>
+      <c r="I311" s="192"/>
+      <c r="J311" s="192"/>
+      <c r="K311" s="192"/>
+      <c r="L311" s="7"/>
+      <c r="M311" s="7"/>
+      <c r="N311" s="7"/>
+      <c r="O311" s="7"/>
+      <c r="P311" s="7"/>
+      <c r="Q311" s="7"/>
+      <c r="R311" s="90"/>
+    </row>
+    <row r="312" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A312" s="85"/>
+      <c r="B312" s="86"/>
+      <c r="C312" s="193"/>
+      <c r="D312" s="86"/>
+      <c r="E312" s="86"/>
+      <c r="F312" s="193"/>
+      <c r="G312" s="86"/>
+      <c r="H312" s="193"/>
+      <c r="I312" s="193"/>
+      <c r="J312" s="193"/>
+      <c r="K312" s="193"/>
+      <c r="L312" s="86"/>
+      <c r="M312" s="86"/>
+      <c r="N312" s="86"/>
+      <c r="O312" s="86"/>
+      <c r="P312" s="86"/>
+      <c r="Q312" s="86"/>
+      <c r="R312" s="129"/>
     </row>
     <row r="315" spans="1:18" ht="14.4" customHeight="1">
       <c r="C315" s="284"/>
@@ -30397,6 +30512,12 @@
     </row>
     <row r="322" spans="3:3" ht="14.4" customHeight="1">
       <c r="C322" s="284"/>
+    </row>
+    <row r="323" spans="3:3" ht="14.4" customHeight="1">
+      <c r="C323" s="284"/>
+    </row>
+    <row r="324" spans="3:3" ht="14.4" customHeight="1">
+      <c r="C324" s="284"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30450,6 +30571,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -30690,27 +30831,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BA7FD74-EE25-42EE-BD44-8280994753BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30727,23 +30867,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>